--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1425,6 +1425,4960 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131501235</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>387569</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6617686</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131501213</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80259</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>387596</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6618070</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131501249</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>392</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>387577</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6618050</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131501250</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>392</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>387571</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6618050</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131501230</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80315</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>387545</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6617619</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131501203</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>387626</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6617753</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131501247</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>392</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>387568</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6618040</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131501195</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91781</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>387619</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6618073</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131501257</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80390</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>387551</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6617617</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131501198</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>387679</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6617717</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131501227</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80315</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>387581</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6617713</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131501229</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80315</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>387557</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6617663</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131501228</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80315</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>387574</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6617698</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131501243</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>392</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>387576</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6617730</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131501216</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80259</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>387664</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6617891</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131501194</v>
+      </c>
+      <c r="B23" t="n">
+        <v>83230</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>387560</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6617541</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131501201</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>392</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>387603</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6617613</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131501224</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80315</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>387594</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6617760</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131501233</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>387666</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6618011</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131501214</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80259</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>387594</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6618061</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131501242</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6441</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Slanklav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Collema flaccidum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>387660</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6617886</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131501239</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>392</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>387579</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6618064</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131501259</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80390</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>387611</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6617519</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131501253</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80390</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>387583</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6618100</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131501211</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>387554</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6617473</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131501223</v>
+      </c>
+      <c r="B33" t="n">
+        <v>83215</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>306</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>387587</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6617454</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131501204</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>387618</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6618118</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131501208</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>387565</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6617589</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131501244</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>392</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>387578</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6617724</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131501246</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>392</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>387628</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6617628</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131501222</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92237</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>387619</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6618071</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131501255</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80390</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>387660</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6617892</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131501238</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>392</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>387572</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6618061</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131501248</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>392</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>387575</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6618043</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131501245</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>392</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>387569</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6617723</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131501234</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>387610</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6617762</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131501240</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>392</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>387597</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6618067</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131501220</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92277</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>387620</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6618075</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131501196</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91781</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>387554</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6617465</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131501209</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>387543</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6617571</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131501212</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80259</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>387577</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6618057</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131501261</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>387569</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6617556</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131501252</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80390</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>387602</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6618110</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131501215</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80259</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>387585</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6618100</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131501226</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80315</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>387577</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6617725</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131501225</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80315</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>387573</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6617731</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131501236</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79250</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>387557</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6617549</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131501210</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>387596</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6617548</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131501263</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>392</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>387610</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6617561</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131501218</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80259</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bergtjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>387575</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6617729</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501235</v>
+        <v>131501213</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>80262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387569</v>
+        <v>387596</v>
       </c>
       <c r="R8" t="n">
-        <v>6617686</v>
+        <v>6618070</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1524,32 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501213</v>
+        <v>131501235</v>
       </c>
       <c r="B9" t="n">
-        <v>80259</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387596</v>
+        <v>387569</v>
       </c>
       <c r="R9" t="n">
-        <v>6618070</v>
+        <v>6617686</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501249</v>
+        <v>131501250</v>
       </c>
       <c r="B10" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387577</v>
+        <v>387571</v>
       </c>
       <c r="R10" t="n">
         <v>6618050</v>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131501250</v>
+        <v>131501249</v>
       </c>
       <c r="B11" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387571</v>
+        <v>387577</v>
       </c>
       <c r="R11" t="n">
         <v>6618050</v>
@@ -1820,7 +1820,7 @@
         <v>131501230</v>
       </c>
       <c r="B12" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>131501203</v>
       </c>
       <c r="B13" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>131501247</v>
       </c>
       <c r="B14" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>131501195</v>
       </c>
       <c r="B15" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>131501257</v>
       </c>
       <c r="B16" t="n">
-        <v>80390</v>
+        <v>80393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131501198</v>
       </c>
       <c r="B17" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>131501227</v>
       </c>
       <c r="B18" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131501229</v>
       </c>
       <c r="B19" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131501228</v>
       </c>
       <c r="B20" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>131501243</v>
       </c>
       <c r="B21" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>131501216</v>
       </c>
       <c r="B22" t="n">
-        <v>80259</v>
+        <v>80262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>131501194</v>
       </c>
       <c r="B23" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>131501201</v>
       </c>
       <c r="B24" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3097,32 +3097,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131501224</v>
+        <v>131501233</v>
       </c>
       <c r="B25" t="n">
-        <v>80315</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387594</v>
+        <v>387666</v>
       </c>
       <c r="R25" t="n">
-        <v>6617760</v>
+        <v>6618011</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3194,32 +3194,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501233</v>
+        <v>131501214</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>80262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387666</v>
+        <v>387594</v>
       </c>
       <c r="R26" t="n">
-        <v>6618011</v>
+        <v>6618061</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501214</v>
+        <v>131501224</v>
       </c>
       <c r="B27" t="n">
-        <v>80259</v>
+        <v>80318</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3329,7 +3329,7 @@
         <v>387594</v>
       </c>
       <c r="R27" t="n">
-        <v>6618061</v>
+        <v>6617760</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501242</v>
+        <v>131501239</v>
       </c>
       <c r="B28" t="n">
-        <v>80223</v>
+        <v>80231</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6441</v>
+        <v>392</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387660</v>
+        <v>387579</v>
       </c>
       <c r="R28" t="n">
-        <v>6617886</v>
+        <v>6618064</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501239</v>
+        <v>131501259</v>
       </c>
       <c r="B29" t="n">
-        <v>80228</v>
+        <v>80393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387579</v>
+        <v>387611</v>
       </c>
       <c r="R29" t="n">
-        <v>6618064</v>
+        <v>6617519</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3565,7 +3565,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3584,10 +3583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501259</v>
+        <v>131501242</v>
       </c>
       <c r="B30" t="n">
-        <v>80390</v>
+        <v>80226</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3595,16 +3594,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6441</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3619,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387611</v>
+        <v>387660</v>
       </c>
       <c r="R30" t="n">
-        <v>6617519</v>
+        <v>6617886</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3663,6 +3662,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3681,10 +3681,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501253</v>
+        <v>131501223</v>
       </c>
       <c r="B31" t="n">
-        <v>80390</v>
+        <v>83218</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3692,21 +3692,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387583</v>
+        <v>387587</v>
       </c>
       <c r="R31" t="n">
-        <v>6618100</v>
+        <v>6617454</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3778,53 +3778,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501211</v>
+        <v>131501253</v>
       </c>
       <c r="B32" t="n">
-        <v>57885</v>
+        <v>80393</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387554</v>
+        <v>387583</v>
       </c>
       <c r="R32" t="n">
-        <v>6617473</v>
+        <v>6618100</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3883,45 +3875,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501223</v>
+        <v>131501208</v>
       </c>
       <c r="B33" t="n">
-        <v>83215</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387587</v>
+        <v>387565</v>
       </c>
       <c r="R33" t="n">
-        <v>6617454</v>
+        <v>6617589</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3954,6 +3954,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3983,7 +3988,7 @@
         <v>131501204</v>
       </c>
       <c r="B34" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4090,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131501208</v>
+        <v>131501211</v>
       </c>
       <c r="B35" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4123,7 +4128,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4133,10 +4138,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>387565</v>
+        <v>387554</v>
       </c>
       <c r="R35" t="n">
-        <v>6617589</v>
+        <v>6617473</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4169,11 +4174,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4203,7 +4203,7 @@
         <v>131501244</v>
       </c>
       <c r="B36" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>131501246</v>
       </c>
       <c r="B37" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>131501222</v>
       </c>
       <c r="B38" t="n">
-        <v>92237</v>
+        <v>92240</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>131501255</v>
       </c>
       <c r="B39" t="n">
-        <v>80390</v>
+        <v>80393</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4594,32 +4594,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131501238</v>
+        <v>131501234</v>
       </c>
       <c r="B40" t="n">
-        <v>80228</v>
+        <v>79253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387572</v>
+        <v>387610</v>
       </c>
       <c r="R40" t="n">
-        <v>6618061</v>
+        <v>6617762</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4673,7 +4673,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4695,7 +4694,7 @@
         <v>131501248</v>
       </c>
       <c r="B41" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4790,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131501245</v>
+        <v>131501238</v>
       </c>
       <c r="B42" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4825,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387569</v>
+        <v>387572</v>
       </c>
       <c r="R42" t="n">
-        <v>6617723</v>
+        <v>6618061</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4888,32 +4887,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501234</v>
+        <v>131501245</v>
       </c>
       <c r="B43" t="n">
-        <v>79250</v>
+        <v>80231</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4923,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387610</v>
+        <v>387569</v>
       </c>
       <c r="R43" t="n">
-        <v>6617762</v>
+        <v>6617723</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4967,6 +4966,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4985,32 +4985,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501240</v>
+        <v>131501196</v>
       </c>
       <c r="B44" t="n">
-        <v>80228</v>
+        <v>91784</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387597</v>
+        <v>387554</v>
       </c>
       <c r="R44" t="n">
-        <v>6618067</v>
+        <v>6617465</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5064,7 +5064,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5083,10 +5082,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501220</v>
+        <v>131501240</v>
       </c>
       <c r="B45" t="n">
-        <v>92277</v>
+        <v>80231</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5094,21 +5093,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>392</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5118,10 +5117,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387620</v>
+        <v>387597</v>
       </c>
       <c r="R45" t="n">
-        <v>6618075</v>
+        <v>6618067</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5162,6 +5161,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5180,32 +5180,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501196</v>
+        <v>131501220</v>
       </c>
       <c r="B46" t="n">
-        <v>91781</v>
+        <v>92280</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387554</v>
+        <v>387620</v>
       </c>
       <c r="R46" t="n">
-        <v>6617465</v>
+        <v>6618075</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5280,7 +5280,7 @@
         <v>131501209</v>
       </c>
       <c r="B47" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131501212</v>
+        <v>131501261</v>
       </c>
       <c r="B48" t="n">
-        <v>80259</v>
+        <v>5177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5398,34 +5398,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R48" t="n">
-        <v>6618057</v>
+        <v>6617556</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5466,6 +5475,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5484,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131501261</v>
+        <v>131501252</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>80393</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5495,43 +5505,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387569</v>
+        <v>387602</v>
       </c>
       <c r="R49" t="n">
-        <v>6617556</v>
+        <v>6618110</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5572,7 +5573,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131501252</v>
+        <v>131501212</v>
       </c>
       <c r="B50" t="n">
-        <v>80390</v>
+        <v>80262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5602,21 +5602,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>387602</v>
+        <v>387577</v>
       </c>
       <c r="R50" t="n">
-        <v>6618110</v>
+        <v>6618057</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5691,7 +5691,7 @@
         <v>131501215</v>
       </c>
       <c r="B51" t="n">
-        <v>80259</v>
+        <v>80262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>131501226</v>
       </c>
       <c r="B52" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>131501225</v>
       </c>
       <c r="B53" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5979,32 +5979,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501236</v>
+        <v>131501218</v>
       </c>
       <c r="B54" t="n">
-        <v>79250</v>
+        <v>80262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387557</v>
+        <v>387575</v>
       </c>
       <c r="R54" t="n">
-        <v>6617549</v>
+        <v>6617729</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501210</v>
+        <v>131501236</v>
       </c>
       <c r="B55" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6087,42 +6087,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387596</v>
+        <v>387557</v>
       </c>
       <c r="R55" t="n">
-        <v>6617548</v>
+        <v>6617549</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6155,11 +6147,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6189,7 +6176,7 @@
         <v>131501263</v>
       </c>
       <c r="B56" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,45 +6271,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131501218</v>
+        <v>131501210</v>
       </c>
       <c r="B57" t="n">
-        <v>80259</v>
+        <v>57888</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>387575</v>
+        <v>387596</v>
       </c>
       <c r="R57" t="n">
-        <v>6617729</v>
+        <v>6617548</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6355,6 +6350,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>131501213</v>
       </c>
       <c r="B8" t="n">
-        <v>80262</v>
+        <v>80263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>131501235</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131501250</v>
       </c>
       <c r="B10" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>131501249</v>
       </c>
       <c r="B11" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,45 +1817,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B12" t="n">
-        <v>80318</v>
+        <v>57889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R12" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1914,53 +1922,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>80319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R13" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131501247</v>
+        <v>131501195</v>
       </c>
       <c r="B14" t="n">
-        <v>80231</v>
+        <v>91785</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387568</v>
+        <v>387619</v>
       </c>
       <c r="R14" t="n">
-        <v>6618040</v>
+        <v>6618073</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2098,7 +2098,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2117,32 +2116,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131501195</v>
+        <v>131501247</v>
       </c>
       <c r="B15" t="n">
-        <v>91784</v>
+        <v>80232</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2152,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387619</v>
+        <v>387568</v>
       </c>
       <c r="R15" t="n">
-        <v>6618073</v>
+        <v>6618040</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2196,6 +2195,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>131501257</v>
       </c>
       <c r="B16" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131501198</v>
       </c>
       <c r="B17" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>131501227</v>
       </c>
       <c r="B18" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131501229</v>
       </c>
       <c r="B19" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131501228</v>
       </c>
       <c r="B20" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,32 +2707,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131501243</v>
+        <v>131501216</v>
       </c>
       <c r="B21" t="n">
-        <v>80231</v>
+        <v>80263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387576</v>
+        <v>387664</v>
       </c>
       <c r="R21" t="n">
-        <v>6617730</v>
+        <v>6617891</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2786,7 +2786,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2805,32 +2804,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131501216</v>
+        <v>131501194</v>
       </c>
       <c r="B22" t="n">
-        <v>80262</v>
+        <v>83234</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387664</v>
+        <v>387560</v>
       </c>
       <c r="R22" t="n">
-        <v>6617891</v>
+        <v>6617541</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2902,32 +2901,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131501194</v>
+        <v>131501201</v>
       </c>
       <c r="B23" t="n">
-        <v>83233</v>
+        <v>80232</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>392</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>387560</v>
+        <v>387603</v>
       </c>
       <c r="R23" t="n">
-        <v>6617541</v>
+        <v>6617613</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2981,6 +2980,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501201</v>
+        <v>131501224</v>
       </c>
       <c r="B24" t="n">
-        <v>80231</v>
+        <v>80319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>392</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387603</v>
+        <v>387594</v>
       </c>
       <c r="R24" t="n">
-        <v>6617613</v>
+        <v>6617760</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3078,7 +3078,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3100,7 +3099,7 @@
         <v>131501233</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,7 +3196,7 @@
         <v>131501214</v>
       </c>
       <c r="B26" t="n">
-        <v>80262</v>
+        <v>80263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501224</v>
+        <v>131501242</v>
       </c>
       <c r="B27" t="n">
-        <v>80318</v>
+        <v>80227</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>6441</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3326,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387594</v>
+        <v>387660</v>
       </c>
       <c r="R27" t="n">
-        <v>6617760</v>
+        <v>6617886</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3370,6 +3369,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3388,32 +3388,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501239</v>
+        <v>131501259</v>
       </c>
       <c r="B28" t="n">
-        <v>80231</v>
+        <v>80394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387579</v>
+        <v>387611</v>
       </c>
       <c r="R28" t="n">
-        <v>6618064</v>
+        <v>6617519</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,7 +3467,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3486,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501259</v>
+        <v>131501239</v>
       </c>
       <c r="B29" t="n">
-        <v>80393</v>
+        <v>80232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3521,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387611</v>
+        <v>387579</v>
       </c>
       <c r="R29" t="n">
-        <v>6617519</v>
+        <v>6618064</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3565,6 +3564,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501242</v>
+        <v>131501253</v>
       </c>
       <c r="B30" t="n">
-        <v>80226</v>
+        <v>80394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3594,16 +3594,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6441</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387660</v>
+        <v>387583</v>
       </c>
       <c r="R30" t="n">
-        <v>6617886</v>
+        <v>6618100</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3662,7 +3662,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3684,7 +3683,7 @@
         <v>131501223</v>
       </c>
       <c r="B31" t="n">
-        <v>83218</v>
+        <v>83219</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,45 +3777,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501253</v>
+        <v>131501204</v>
       </c>
       <c r="B32" t="n">
-        <v>80393</v>
+        <v>57889</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387583</v>
+        <v>387618</v>
       </c>
       <c r="R32" t="n">
-        <v>6618100</v>
+        <v>6618118</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3849,6 +3856,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3878,7 +3890,7 @@
         <v>131501208</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,10 +3997,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501204</v>
+        <v>131501211</v>
       </c>
       <c r="B34" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4018,7 +4030,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4028,10 +4040,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387618</v>
+        <v>387554</v>
       </c>
       <c r="R34" t="n">
-        <v>6618118</v>
+        <v>6617473</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4064,11 +4076,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4095,53 +4102,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131501211</v>
+        <v>131501244</v>
       </c>
       <c r="B35" t="n">
-        <v>57888</v>
+        <v>80232</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>387554</v>
+        <v>387578</v>
       </c>
       <c r="R35" t="n">
-        <v>6617473</v>
+        <v>6617724</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4182,6 +4181,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4200,10 +4200,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131501244</v>
+        <v>131501246</v>
       </c>
       <c r="B36" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>387578</v>
+        <v>387628</v>
       </c>
       <c r="R36" t="n">
-        <v>6617724</v>
+        <v>6617628</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4298,45 +4298,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131501246</v>
+        <v>131501222</v>
       </c>
       <c r="B37" t="n">
-        <v>80231</v>
+        <v>92241</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>392</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387628</v>
+        <v>387619</v>
       </c>
       <c r="R37" t="n">
-        <v>6617628</v>
+        <v>6618071</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4396,48 +4399,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131501222</v>
+        <v>131501255</v>
       </c>
       <c r="B38" t="n">
-        <v>92240</v>
+        <v>80394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387619</v>
+        <v>387660</v>
       </c>
       <c r="R38" t="n">
-        <v>6618071</v>
+        <v>6617892</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4478,7 +4478,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4497,27 +4496,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131501255</v>
+        <v>131501234</v>
       </c>
       <c r="B39" t="n">
-        <v>80393</v>
+        <v>79254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4532,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387660</v>
+        <v>387610</v>
       </c>
       <c r="R39" t="n">
-        <v>6617892</v>
+        <v>6617762</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4594,32 +4593,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131501234</v>
+        <v>131501248</v>
       </c>
       <c r="B40" t="n">
-        <v>79253</v>
+        <v>80232</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4629,10 +4628,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387610</v>
+        <v>387575</v>
       </c>
       <c r="R40" t="n">
-        <v>6617762</v>
+        <v>6618043</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4673,6 +4672,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131501248</v>
+        <v>131501238</v>
       </c>
       <c r="B41" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387575</v>
+        <v>387572</v>
       </c>
       <c r="R41" t="n">
-        <v>6618043</v>
+        <v>6618061</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131501238</v>
+        <v>131501245</v>
       </c>
       <c r="B42" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387572</v>
+        <v>387569</v>
       </c>
       <c r="R42" t="n">
-        <v>6618061</v>
+        <v>6617723</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501245</v>
+        <v>131501240</v>
       </c>
       <c r="B43" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387569</v>
+        <v>387597</v>
       </c>
       <c r="R43" t="n">
-        <v>6617723</v>
+        <v>6618067</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4988,7 +4988,7 @@
         <v>131501196</v>
       </c>
       <c r="B44" t="n">
-        <v>91784</v>
+        <v>91785</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501240</v>
+        <v>131501220</v>
       </c>
       <c r="B45" t="n">
-        <v>80231</v>
+        <v>92281</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,21 +5093,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>392</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387597</v>
+        <v>387620</v>
       </c>
       <c r="R45" t="n">
-        <v>6618067</v>
+        <v>6618075</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5161,7 +5161,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5180,45 +5179,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501220</v>
+        <v>131501209</v>
       </c>
       <c r="B46" t="n">
-        <v>92280</v>
+        <v>57889</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387620</v>
+        <v>387543</v>
       </c>
       <c r="R46" t="n">
-        <v>6618075</v>
+        <v>6617571</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5251,6 +5258,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5277,53 +5289,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131501209</v>
+        <v>131501212</v>
       </c>
       <c r="B47" t="n">
-        <v>57888</v>
+        <v>80263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387543</v>
+        <v>387577</v>
       </c>
       <c r="R47" t="n">
-        <v>6617571</v>
+        <v>6618057</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5356,11 +5360,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5387,10 +5386,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131501261</v>
+        <v>131501252</v>
       </c>
       <c r="B48" t="n">
-        <v>5177</v>
+        <v>80394</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5398,43 +5397,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387569</v>
+        <v>387602</v>
       </c>
       <c r="R48" t="n">
-        <v>6617556</v>
+        <v>6618110</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5475,7 +5465,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5494,10 +5483,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131501252</v>
+        <v>131501261</v>
       </c>
       <c r="B49" t="n">
-        <v>80393</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5505,34 +5494,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387602</v>
+        <v>387569</v>
       </c>
       <c r="R49" t="n">
-        <v>6618110</v>
+        <v>6617556</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5573,6 +5571,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5591,10 +5590,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131501212</v>
+        <v>131501215</v>
       </c>
       <c r="B50" t="n">
-        <v>80262</v>
+        <v>80263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5626,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>387577</v>
+        <v>387585</v>
       </c>
       <c r="R50" t="n">
-        <v>6618057</v>
+        <v>6618100</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5688,10 +5687,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131501215</v>
+        <v>131501226</v>
       </c>
       <c r="B51" t="n">
-        <v>80262</v>
+        <v>80319</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5699,21 +5698,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5723,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>387585</v>
+        <v>387577</v>
       </c>
       <c r="R51" t="n">
-        <v>6618100</v>
+        <v>6617725</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5785,10 +5784,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131501226</v>
+        <v>131501225</v>
       </c>
       <c r="B52" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5820,10 +5819,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>387577</v>
+        <v>387573</v>
       </c>
       <c r="R52" t="n">
-        <v>6617725</v>
+        <v>6617731</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5882,10 +5881,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501225</v>
+        <v>131501218</v>
       </c>
       <c r="B53" t="n">
-        <v>80318</v>
+        <v>80263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5893,21 +5892,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5917,10 +5916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387573</v>
+        <v>387575</v>
       </c>
       <c r="R53" t="n">
-        <v>6617731</v>
+        <v>6617729</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5979,32 +5978,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501218</v>
+        <v>131501236</v>
       </c>
       <c r="B54" t="n">
-        <v>80262</v>
+        <v>79254</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6014,10 +6013,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387575</v>
+        <v>387557</v>
       </c>
       <c r="R54" t="n">
-        <v>6617729</v>
+        <v>6617549</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6076,32 +6075,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501236</v>
+        <v>131501263</v>
       </c>
       <c r="B55" t="n">
-        <v>79253</v>
+        <v>80232</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6111,10 +6110,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387557</v>
+        <v>387610</v>
       </c>
       <c r="R55" t="n">
-        <v>6617549</v>
+        <v>6617561</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6155,6 +6154,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6173,45 +6173,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501263</v>
+        <v>131501210</v>
       </c>
       <c r="B56" t="n">
-        <v>80231</v>
+        <v>57889</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387610</v>
+        <v>387596</v>
       </c>
       <c r="R56" t="n">
-        <v>6617561</v>
+        <v>6617548</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6246,13 +6254,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6271,53 +6283,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131501210</v>
+        <v>131501193</v>
       </c>
       <c r="B57" t="n">
-        <v>57888</v>
+        <v>80232</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>387596</v>
+        <v>387616</v>
       </c>
       <c r="R57" t="n">
-        <v>6617548</v>
+        <v>6617521</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6352,17 +6356,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131501195</v>
+        <v>131501247</v>
       </c>
       <c r="B14" t="n">
-        <v>91785</v>
+        <v>80232</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387619</v>
+        <v>387568</v>
       </c>
       <c r="R14" t="n">
-        <v>6618073</v>
+        <v>6618040</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2098,6 +2098,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2116,32 +2117,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131501247</v>
+        <v>131501195</v>
       </c>
       <c r="B15" t="n">
-        <v>80232</v>
+        <v>91785</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387568</v>
+        <v>387619</v>
       </c>
       <c r="R15" t="n">
-        <v>6618040</v>
+        <v>6618073</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2195,7 +2196,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131501212</v>
+        <v>131501261</v>
       </c>
       <c r="B47" t="n">
-        <v>80263</v>
+        <v>5177</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,34 +5300,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R47" t="n">
-        <v>6618057</v>
+        <v>6617556</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5368,6 +5377,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5386,10 +5396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131501252</v>
+        <v>131501212</v>
       </c>
       <c r="B48" t="n">
-        <v>80394</v>
+        <v>80263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5397,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5421,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387602</v>
+        <v>387577</v>
       </c>
       <c r="R48" t="n">
-        <v>6618110</v>
+        <v>6618057</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5483,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131501261</v>
+        <v>131501252</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>80394</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5494,43 +5504,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387569</v>
+        <v>387602</v>
       </c>
       <c r="R49" t="n">
-        <v>6617556</v>
+        <v>6618110</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5571,7 +5572,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501213</v>
+        <v>131501250</v>
       </c>
       <c r="B8" t="n">
-        <v>80263</v>
+        <v>80238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387596</v>
+        <v>387571</v>
       </c>
       <c r="R8" t="n">
-        <v>6618070</v>
+        <v>6618050</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1506,6 +1506,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1524,32 +1525,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501235</v>
+        <v>131501249</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>80238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387569</v>
+        <v>387577</v>
       </c>
       <c r="R9" t="n">
-        <v>6617686</v>
+        <v>6618050</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1603,6 +1604,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1621,32 +1623,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501250</v>
+        <v>131501235</v>
       </c>
       <c r="B10" t="n">
-        <v>80232</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387571</v>
+        <v>387569</v>
       </c>
       <c r="R10" t="n">
-        <v>6618050</v>
+        <v>6617686</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1700,7 +1702,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1719,32 +1720,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131501249</v>
+        <v>131501213</v>
       </c>
       <c r="B11" t="n">
-        <v>80232</v>
+        <v>80269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387577</v>
+        <v>387596</v>
       </c>
       <c r="R11" t="n">
-        <v>6618050</v>
+        <v>6618070</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1798,7 +1799,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>131501203</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>131501230</v>
       </c>
       <c r="B13" t="n">
-        <v>80319</v>
+        <v>80325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>131501247</v>
       </c>
       <c r="B14" t="n">
-        <v>80232</v>
+        <v>80238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>131501195</v>
       </c>
       <c r="B15" t="n">
-        <v>91785</v>
+        <v>91791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>131501257</v>
       </c>
       <c r="B16" t="n">
-        <v>80394</v>
+        <v>80400</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131501198</v>
       </c>
       <c r="B17" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>131501227</v>
       </c>
       <c r="B18" t="n">
-        <v>80319</v>
+        <v>80325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131501229</v>
       </c>
       <c r="B19" t="n">
-        <v>80319</v>
+        <v>80325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131501228</v>
       </c>
       <c r="B20" t="n">
-        <v>80319</v>
+        <v>80325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>131501216</v>
       </c>
       <c r="B21" t="n">
-        <v>80263</v>
+        <v>80269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>131501194</v>
       </c>
       <c r="B22" t="n">
-        <v>83234</v>
+        <v>83240</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>131501201</v>
       </c>
       <c r="B23" t="n">
-        <v>80232</v>
+        <v>80238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501224</v>
+        <v>131501233</v>
       </c>
       <c r="B24" t="n">
-        <v>80319</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387594</v>
+        <v>387666</v>
       </c>
       <c r="R24" t="n">
-        <v>6617760</v>
+        <v>6618011</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3096,32 +3096,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131501233</v>
+        <v>131501214</v>
       </c>
       <c r="B25" t="n">
-        <v>79254</v>
+        <v>80269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387666</v>
+        <v>387594</v>
       </c>
       <c r="R25" t="n">
-        <v>6618011</v>
+        <v>6618061</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501214</v>
+        <v>131501224</v>
       </c>
       <c r="B26" t="n">
-        <v>80263</v>
+        <v>80325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
         <v>387594</v>
       </c>
       <c r="R26" t="n">
-        <v>6618061</v>
+        <v>6617760</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501242</v>
+        <v>131501239</v>
       </c>
       <c r="B27" t="n">
-        <v>80227</v>
+        <v>80238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6441</v>
+        <v>392</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387660</v>
+        <v>387579</v>
       </c>
       <c r="R27" t="n">
-        <v>6617886</v>
+        <v>6618064</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501259</v>
+        <v>131501242</v>
       </c>
       <c r="B28" t="n">
-        <v>80394</v>
+        <v>80233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6441</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387611</v>
+        <v>387660</v>
       </c>
       <c r="R28" t="n">
-        <v>6617519</v>
+        <v>6617886</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,6 +3467,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,32 +3486,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501239</v>
+        <v>131501259</v>
       </c>
       <c r="B29" t="n">
-        <v>80232</v>
+        <v>80400</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3521,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387579</v>
+        <v>387611</v>
       </c>
       <c r="R29" t="n">
-        <v>6618064</v>
+        <v>6617519</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3564,7 +3565,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3583,45 +3583,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501253</v>
+        <v>131501208</v>
       </c>
       <c r="B30" t="n">
-        <v>80394</v>
+        <v>57895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387583</v>
+        <v>387565</v>
       </c>
       <c r="R30" t="n">
-        <v>6618100</v>
+        <v>6617589</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3654,6 +3662,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3680,45 +3693,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501223</v>
+        <v>131501204</v>
       </c>
       <c r="B31" t="n">
-        <v>83219</v>
+        <v>57895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387587</v>
+        <v>387618</v>
       </c>
       <c r="R31" t="n">
-        <v>6617454</v>
+        <v>6618118</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3751,6 +3772,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3777,10 +3803,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501204</v>
+        <v>131501211</v>
       </c>
       <c r="B32" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3810,7 +3836,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3820,10 +3846,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387618</v>
+        <v>387554</v>
       </c>
       <c r="R32" t="n">
-        <v>6618118</v>
+        <v>6617473</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3856,11 +3882,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3887,53 +3908,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501208</v>
+        <v>131501253</v>
       </c>
       <c r="B33" t="n">
-        <v>57889</v>
+        <v>80400</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387565</v>
+        <v>387583</v>
       </c>
       <c r="R33" t="n">
-        <v>6617589</v>
+        <v>6618100</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3966,11 +3979,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3997,53 +4005,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501211</v>
+        <v>131501223</v>
       </c>
       <c r="B34" t="n">
-        <v>57889</v>
+        <v>83225</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387554</v>
+        <v>387587</v>
       </c>
       <c r="R34" t="n">
-        <v>6617473</v>
+        <v>6617454</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4105,7 +4105,7 @@
         <v>131501244</v>
       </c>
       <c r="B35" t="n">
-        <v>80232</v>
+        <v>80238</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>131501246</v>
       </c>
       <c r="B36" t="n">
-        <v>80232</v>
+        <v>80238</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4298,48 +4298,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131501222</v>
+        <v>131501255</v>
       </c>
       <c r="B37" t="n">
-        <v>92241</v>
+        <v>80400</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387619</v>
+        <v>387660</v>
       </c>
       <c r="R37" t="n">
-        <v>6618071</v>
+        <v>6617892</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4380,7 +4377,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4399,45 +4395,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131501255</v>
+        <v>131501222</v>
       </c>
       <c r="B38" t="n">
-        <v>80394</v>
+        <v>92247</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6040186</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387660</v>
+        <v>387619</v>
       </c>
       <c r="R38" t="n">
-        <v>6617892</v>
+        <v>6618071</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4478,6 +4477,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>131501234</v>
       </c>
       <c r="B39" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>131501248</v>
       </c>
       <c r="B40" t="n">
-        <v>80232</v>
+        <v>80238</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>131501238</v>
       </c>
       <c r="B41" t="n">
-        <v>80232</v>
+        <v>80238</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>131501245</v>
       </c>
       <c r="B42" t="n">
-        <v>80232</v>
+        <v>80238</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501240</v>
+        <v>131501196</v>
       </c>
       <c r="B43" t="n">
-        <v>80232</v>
+        <v>91791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387597</v>
+        <v>387554</v>
       </c>
       <c r="R43" t="n">
-        <v>6618067</v>
+        <v>6617465</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4966,7 +4966,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4985,32 +4984,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501196</v>
+        <v>131501240</v>
       </c>
       <c r="B44" t="n">
-        <v>91785</v>
+        <v>80238</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5020,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387554</v>
+        <v>387597</v>
       </c>
       <c r="R44" t="n">
-        <v>6617465</v>
+        <v>6618067</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5064,6 +5063,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>131501220</v>
       </c>
       <c r="B45" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>131501209</v>
       </c>
       <c r="B46" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131501261</v>
+        <v>131501212</v>
       </c>
       <c r="B47" t="n">
-        <v>5177</v>
+        <v>80269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,43 +5300,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387569</v>
+        <v>387577</v>
       </c>
       <c r="R47" t="n">
-        <v>6617556</v>
+        <v>6618057</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5377,7 +5368,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5396,10 +5386,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131501212</v>
+        <v>131501252</v>
       </c>
       <c r="B48" t="n">
-        <v>80263</v>
+        <v>80400</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,21 +5397,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5421,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387577</v>
+        <v>387602</v>
       </c>
       <c r="R48" t="n">
-        <v>6618057</v>
+        <v>6618110</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5493,10 +5483,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131501252</v>
+        <v>131501261</v>
       </c>
       <c r="B49" t="n">
-        <v>80394</v>
+        <v>5177</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5504,34 +5494,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387602</v>
+        <v>387569</v>
       </c>
       <c r="R49" t="n">
-        <v>6618110</v>
+        <v>6617556</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5572,6 +5571,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>131501215</v>
       </c>
       <c r="B50" t="n">
-        <v>80263</v>
+        <v>80269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>131501226</v>
       </c>
       <c r="B51" t="n">
-        <v>80319</v>
+        <v>80325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131501225</v>
       </c>
       <c r="B52" t="n">
-        <v>80319</v>
+        <v>80325</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5881,45 +5881,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501218</v>
+        <v>131501210</v>
       </c>
       <c r="B53" t="n">
-        <v>80263</v>
+        <v>57895</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387575</v>
+        <v>387596</v>
       </c>
       <c r="R53" t="n">
-        <v>6617729</v>
+        <v>6617548</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5952,6 +5960,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5978,32 +5991,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501236</v>
+        <v>131501218</v>
       </c>
       <c r="B54" t="n">
-        <v>79254</v>
+        <v>80269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6013,10 +6026,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387557</v>
+        <v>387575</v>
       </c>
       <c r="R54" t="n">
-        <v>6617549</v>
+        <v>6617729</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6075,32 +6088,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501263</v>
+        <v>131501236</v>
       </c>
       <c r="B55" t="n">
-        <v>80232</v>
+        <v>79260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6110,10 +6123,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387610</v>
+        <v>387557</v>
       </c>
       <c r="R55" t="n">
-        <v>6617561</v>
+        <v>6617549</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6154,7 +6167,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6173,53 +6185,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501210</v>
+        <v>131501263</v>
       </c>
       <c r="B56" t="n">
-        <v>57889</v>
+        <v>80238</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387596</v>
+        <v>387610</v>
       </c>
       <c r="R56" t="n">
-        <v>6617548</v>
+        <v>6617561</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6254,17 +6258,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>131501193</v>
       </c>
       <c r="B57" t="n">
-        <v>80232</v>
+        <v>80238</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -4298,45 +4298,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131501255</v>
+        <v>131501222</v>
       </c>
       <c r="B37" t="n">
-        <v>80400</v>
+        <v>92247</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387660</v>
+        <v>387619</v>
       </c>
       <c r="R37" t="n">
-        <v>6617892</v>
+        <v>6618071</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4377,6 +4380,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4395,48 +4399,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131501222</v>
+        <v>131501255</v>
       </c>
       <c r="B38" t="n">
-        <v>92247</v>
+        <v>80400</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387619</v>
+        <v>387660</v>
       </c>
       <c r="R38" t="n">
-        <v>6618071</v>
+        <v>6617892</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4477,7 +4478,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501250</v>
+        <v>131501213</v>
       </c>
       <c r="B8" t="n">
-        <v>80238</v>
+        <v>80269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387571</v>
+        <v>387596</v>
       </c>
       <c r="R8" t="n">
-        <v>6618050</v>
+        <v>6618070</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1506,7 +1506,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1525,32 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501249</v>
+        <v>131501235</v>
       </c>
       <c r="B9" t="n">
-        <v>80238</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1560,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R9" t="n">
-        <v>6618050</v>
+        <v>6617686</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1604,7 +1603,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1623,32 +1621,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501235</v>
+        <v>131501250</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>80238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1658,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387569</v>
+        <v>387571</v>
       </c>
       <c r="R10" t="n">
-        <v>6617686</v>
+        <v>6618050</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1702,6 +1700,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1720,32 +1719,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131501213</v>
+        <v>131501249</v>
       </c>
       <c r="B11" t="n">
-        <v>80269</v>
+        <v>80238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387596</v>
+        <v>387577</v>
       </c>
       <c r="R11" t="n">
-        <v>6618070</v>
+        <v>6618050</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1799,6 +1798,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131501247</v>
+        <v>131501195</v>
       </c>
       <c r="B14" t="n">
-        <v>80238</v>
+        <v>91791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387568</v>
+        <v>387619</v>
       </c>
       <c r="R14" t="n">
-        <v>6618040</v>
+        <v>6618073</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2098,7 +2098,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2117,32 +2116,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131501195</v>
+        <v>131501247</v>
       </c>
       <c r="B15" t="n">
-        <v>91791</v>
+        <v>80238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2152,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387619</v>
+        <v>387568</v>
       </c>
       <c r="R15" t="n">
-        <v>6618073</v>
+        <v>6618040</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2196,6 +2195,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131501227</v>
+        <v>131501229</v>
       </c>
       <c r="B18" t="n">
         <v>80325</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387581</v>
+        <v>387557</v>
       </c>
       <c r="R18" t="n">
-        <v>6617713</v>
+        <v>6617663</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131501229</v>
+        <v>131501227</v>
       </c>
       <c r="B19" t="n">
         <v>80325</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387557</v>
+        <v>387581</v>
       </c>
       <c r="R19" t="n">
-        <v>6617663</v>
+        <v>6617713</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501239</v>
+        <v>131501242</v>
       </c>
       <c r="B27" t="n">
-        <v>80238</v>
+        <v>80233</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>392</v>
+        <v>6441</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387579</v>
+        <v>387660</v>
       </c>
       <c r="R27" t="n">
-        <v>6618064</v>
+        <v>6617886</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501242</v>
+        <v>131501259</v>
       </c>
       <c r="B28" t="n">
-        <v>80233</v>
+        <v>80400</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6441</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387660</v>
+        <v>387611</v>
       </c>
       <c r="R28" t="n">
-        <v>6617886</v>
+        <v>6617519</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,7 +3467,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3486,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501259</v>
+        <v>131501239</v>
       </c>
       <c r="B29" t="n">
-        <v>80400</v>
+        <v>80238</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3521,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387611</v>
+        <v>387579</v>
       </c>
       <c r="R29" t="n">
-        <v>6617519</v>
+        <v>6618064</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3565,6 +3564,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4298,48 +4298,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131501222</v>
+        <v>131501255</v>
       </c>
       <c r="B37" t="n">
-        <v>92247</v>
+        <v>80400</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387619</v>
+        <v>387660</v>
       </c>
       <c r="R37" t="n">
-        <v>6618071</v>
+        <v>6617892</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4380,7 +4377,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4399,45 +4395,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131501255</v>
+        <v>131501222</v>
       </c>
       <c r="B38" t="n">
-        <v>80400</v>
+        <v>92247</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6040186</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387660</v>
+        <v>387619</v>
       </c>
       <c r="R38" t="n">
-        <v>6617892</v>
+        <v>6618071</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4478,6 +4477,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501196</v>
+        <v>131501220</v>
       </c>
       <c r="B43" t="n">
-        <v>91791</v>
+        <v>92287</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387554</v>
+        <v>387620</v>
       </c>
       <c r="R43" t="n">
-        <v>6617465</v>
+        <v>6618075</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4984,32 +4984,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501240</v>
+        <v>131501196</v>
       </c>
       <c r="B44" t="n">
-        <v>80238</v>
+        <v>91791</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387597</v>
+        <v>387554</v>
       </c>
       <c r="R44" t="n">
-        <v>6618067</v>
+        <v>6617465</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5063,7 +5063,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5082,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501220</v>
+        <v>131501240</v>
       </c>
       <c r="B45" t="n">
-        <v>92287</v>
+        <v>80238</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,21 +5092,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>392</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5117,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387620</v>
+        <v>387597</v>
       </c>
       <c r="R45" t="n">
-        <v>6618075</v>
+        <v>6618067</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5161,6 +5160,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5881,53 +5881,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501210</v>
+        <v>131501263</v>
       </c>
       <c r="B53" t="n">
-        <v>57895</v>
+        <v>80238</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387596</v>
+        <v>387610</v>
       </c>
       <c r="R53" t="n">
-        <v>6617548</v>
+        <v>6617561</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5962,17 +5954,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6185,45 +6173,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501263</v>
+        <v>131501210</v>
       </c>
       <c r="B56" t="n">
-        <v>80238</v>
+        <v>57895</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387610</v>
+        <v>387596</v>
       </c>
       <c r="R56" t="n">
-        <v>6617561</v>
+        <v>6617548</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6258,13 +6254,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501213</v>
+        <v>131501250</v>
       </c>
       <c r="B8" t="n">
-        <v>80269</v>
+        <v>80238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387596</v>
+        <v>387571</v>
       </c>
       <c r="R8" t="n">
-        <v>6618070</v>
+        <v>6618050</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1506,6 +1506,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1524,32 +1525,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501235</v>
+        <v>131501249</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>80238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387569</v>
+        <v>387577</v>
       </c>
       <c r="R9" t="n">
-        <v>6617686</v>
+        <v>6618050</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1603,6 +1604,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1621,32 +1623,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501250</v>
+        <v>131501213</v>
       </c>
       <c r="B10" t="n">
-        <v>80238</v>
+        <v>80269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387571</v>
+        <v>387596</v>
       </c>
       <c r="R10" t="n">
-        <v>6618050</v>
+        <v>6618070</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1700,7 +1702,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1719,32 +1720,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131501249</v>
+        <v>131501235</v>
       </c>
       <c r="B11" t="n">
-        <v>80238</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R11" t="n">
-        <v>6618050</v>
+        <v>6617686</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1798,7 +1799,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501242</v>
+        <v>131501239</v>
       </c>
       <c r="B27" t="n">
-        <v>80233</v>
+        <v>80238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6441</v>
+        <v>392</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387660</v>
+        <v>387579</v>
       </c>
       <c r="R27" t="n">
-        <v>6617886</v>
+        <v>6618064</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501259</v>
+        <v>131501242</v>
       </c>
       <c r="B28" t="n">
-        <v>80400</v>
+        <v>80233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6441</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387611</v>
+        <v>387660</v>
       </c>
       <c r="R28" t="n">
-        <v>6617519</v>
+        <v>6617886</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,6 +3467,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,32 +3486,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501239</v>
+        <v>131501259</v>
       </c>
       <c r="B29" t="n">
-        <v>80238</v>
+        <v>80400</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3521,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387579</v>
+        <v>387611</v>
       </c>
       <c r="R29" t="n">
-        <v>6618064</v>
+        <v>6617519</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3564,7 +3565,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -5979,45 +5979,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501218</v>
+        <v>131501210</v>
       </c>
       <c r="B54" t="n">
-        <v>80269</v>
+        <v>57895</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387575</v>
+        <v>387596</v>
       </c>
       <c r="R54" t="n">
-        <v>6617729</v>
+        <v>6617548</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6050,6 +6058,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6076,32 +6089,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501236</v>
+        <v>131501218</v>
       </c>
       <c r="B55" t="n">
-        <v>79260</v>
+        <v>80269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6111,10 +6124,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387557</v>
+        <v>387575</v>
       </c>
       <c r="R55" t="n">
-        <v>6617549</v>
+        <v>6617729</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6173,10 +6186,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501210</v>
+        <v>131501236</v>
       </c>
       <c r="B56" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6184,42 +6197,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387596</v>
+        <v>387557</v>
       </c>
       <c r="R56" t="n">
-        <v>6617548</v>
+        <v>6617549</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6252,11 +6257,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,7 +1427,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501250</v>
+        <v>131501249</v>
       </c>
       <c r="B8" t="n">
         <v>80238</v>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387571</v>
+        <v>387577</v>
       </c>
       <c r="R8" t="n">
         <v>6618050</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501249</v>
+        <v>131501250</v>
       </c>
       <c r="B9" t="n">
         <v>80238</v>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387577</v>
+        <v>387571</v>
       </c>
       <c r="R9" t="n">
         <v>6618050</v>
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131501195</v>
+        <v>131501247</v>
       </c>
       <c r="B14" t="n">
-        <v>91791</v>
+        <v>80238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387619</v>
+        <v>387568</v>
       </c>
       <c r="R14" t="n">
-        <v>6618073</v>
+        <v>6618040</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2098,6 +2098,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2116,32 +2117,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131501247</v>
+        <v>131501195</v>
       </c>
       <c r="B15" t="n">
-        <v>80238</v>
+        <v>91791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387568</v>
+        <v>387619</v>
       </c>
       <c r="R15" t="n">
-        <v>6618040</v>
+        <v>6618073</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2195,7 +2196,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B16" t="n">
-        <v>80400</v>
+        <v>57086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,34 +2225,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R16" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2311,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B17" t="n">
-        <v>57086</v>
+        <v>80400</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,42 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R17" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131501229</v>
+        <v>131501227</v>
       </c>
       <c r="B18" t="n">
         <v>80325</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387557</v>
+        <v>387581</v>
       </c>
       <c r="R18" t="n">
-        <v>6617663</v>
+        <v>6617713</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131501227</v>
+        <v>131501229</v>
       </c>
       <c r="B19" t="n">
         <v>80325</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387581</v>
+        <v>387557</v>
       </c>
       <c r="R19" t="n">
-        <v>6617713</v>
+        <v>6617663</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -3583,53 +3583,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501208</v>
+        <v>131501223</v>
       </c>
       <c r="B30" t="n">
-        <v>57895</v>
+        <v>83225</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387565</v>
+        <v>387587</v>
       </c>
       <c r="R30" t="n">
-        <v>6617589</v>
+        <v>6617454</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3662,11 +3654,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3693,53 +3680,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501204</v>
+        <v>131501253</v>
       </c>
       <c r="B31" t="n">
-        <v>57895</v>
+        <v>80400</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387618</v>
+        <v>387583</v>
       </c>
       <c r="R31" t="n">
-        <v>6618118</v>
+        <v>6618100</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3772,11 +3751,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3803,7 +3777,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501211</v>
+        <v>131501208</v>
       </c>
       <c r="B32" t="n">
         <v>57895</v>
@@ -3836,7 +3810,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3846,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387554</v>
+        <v>387565</v>
       </c>
       <c r="R32" t="n">
-        <v>6617473</v>
+        <v>6617589</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3882,6 +3856,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,45 +3887,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501253</v>
+        <v>131501204</v>
       </c>
       <c r="B33" t="n">
-        <v>80400</v>
+        <v>57895</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387583</v>
+        <v>387618</v>
       </c>
       <c r="R33" t="n">
-        <v>6618100</v>
+        <v>6618118</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3979,6 +3966,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4005,45 +3997,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501223</v>
+        <v>131501211</v>
       </c>
       <c r="B34" t="n">
-        <v>83225</v>
+        <v>57895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387587</v>
+        <v>387554</v>
       </c>
       <c r="R34" t="n">
-        <v>6617454</v>
+        <v>6617473</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4398,7 +4398,7 @@
         <v>131501222</v>
       </c>
       <c r="B38" t="n">
-        <v>92247</v>
+        <v>92248</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131501234</v>
+        <v>131501238</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>80238</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387610</v>
+        <v>387572</v>
       </c>
       <c r="R39" t="n">
-        <v>6617762</v>
+        <v>6618061</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4575,6 +4575,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4691,7 +4692,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131501238</v>
+        <v>131501245</v>
       </c>
       <c r="B41" t="n">
         <v>80238</v>
@@ -4726,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387572</v>
+        <v>387569</v>
       </c>
       <c r="R41" t="n">
-        <v>6618061</v>
+        <v>6617723</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4789,32 +4790,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131501245</v>
+        <v>131501234</v>
       </c>
       <c r="B42" t="n">
-        <v>80238</v>
+        <v>79260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387569</v>
+        <v>387610</v>
       </c>
       <c r="R42" t="n">
-        <v>6617723</v>
+        <v>6617762</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4868,7 +4869,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501220</v>
+        <v>131501240</v>
       </c>
       <c r="B43" t="n">
-        <v>92287</v>
+        <v>80238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,21 +4898,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>392</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387620</v>
+        <v>387597</v>
       </c>
       <c r="R43" t="n">
-        <v>6618075</v>
+        <v>6618067</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4966,6 +4966,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4984,32 +4985,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501196</v>
+        <v>131501220</v>
       </c>
       <c r="B44" t="n">
-        <v>91791</v>
+        <v>92288</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,10 +5020,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387554</v>
+        <v>387620</v>
       </c>
       <c r="R44" t="n">
-        <v>6617465</v>
+        <v>6618075</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5081,45 +5082,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501240</v>
+        <v>131501209</v>
       </c>
       <c r="B45" t="n">
-        <v>80238</v>
+        <v>57895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387597</v>
+        <v>387543</v>
       </c>
       <c r="R45" t="n">
-        <v>6618067</v>
+        <v>6617571</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5154,13 +5163,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5179,53 +5192,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501209</v>
+        <v>131501196</v>
       </c>
       <c r="B46" t="n">
-        <v>57895</v>
+        <v>91791</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387543</v>
+        <v>387554</v>
       </c>
       <c r="R46" t="n">
-        <v>6617571</v>
+        <v>6617465</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5258,11 +5263,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131501212</v>
+        <v>131501261</v>
       </c>
       <c r="B47" t="n">
-        <v>80269</v>
+        <v>5177</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,34 +5300,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R47" t="n">
-        <v>6618057</v>
+        <v>6617556</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5368,6 +5377,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5386,10 +5396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131501252</v>
+        <v>131501212</v>
       </c>
       <c r="B48" t="n">
-        <v>80400</v>
+        <v>80269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5397,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5421,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387602</v>
+        <v>387577</v>
       </c>
       <c r="R48" t="n">
-        <v>6618110</v>
+        <v>6618057</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5483,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131501261</v>
+        <v>131501252</v>
       </c>
       <c r="B49" t="n">
-        <v>5177</v>
+        <v>80400</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5494,43 +5504,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387569</v>
+        <v>387602</v>
       </c>
       <c r="R49" t="n">
-        <v>6617556</v>
+        <v>6618110</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5571,7 +5572,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5979,53 +5979,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501210</v>
+        <v>131501218</v>
       </c>
       <c r="B54" t="n">
-        <v>57895</v>
+        <v>80269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387596</v>
+        <v>387575</v>
       </c>
       <c r="R54" t="n">
-        <v>6617548</v>
+        <v>6617729</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6058,11 +6050,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6089,32 +6076,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501218</v>
+        <v>131501236</v>
       </c>
       <c r="B55" t="n">
-        <v>80269</v>
+        <v>79260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6124,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387575</v>
+        <v>387557</v>
       </c>
       <c r="R55" t="n">
-        <v>6617729</v>
+        <v>6617549</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6186,10 +6173,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501236</v>
+        <v>131501210</v>
       </c>
       <c r="B56" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6197,34 +6184,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387557</v>
+        <v>387596</v>
       </c>
       <c r="R56" t="n">
-        <v>6617549</v>
+        <v>6617548</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6257,6 +6252,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501249</v>
+        <v>131501213</v>
       </c>
       <c r="B8" t="n">
-        <v>80238</v>
+        <v>80270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387577</v>
+        <v>387596</v>
       </c>
       <c r="R8" t="n">
-        <v>6618050</v>
+        <v>6618070</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1506,7 +1506,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1525,32 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501250</v>
+        <v>131501235</v>
       </c>
       <c r="B9" t="n">
-        <v>80238</v>
+        <v>79261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1560,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387571</v>
+        <v>387569</v>
       </c>
       <c r="R9" t="n">
-        <v>6618050</v>
+        <v>6617686</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1604,7 +1603,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1623,32 +1621,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501213</v>
+        <v>131501250</v>
       </c>
       <c r="B10" t="n">
-        <v>80269</v>
+        <v>80239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1658,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387596</v>
+        <v>387571</v>
       </c>
       <c r="R10" t="n">
-        <v>6618070</v>
+        <v>6618050</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1702,6 +1700,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1720,32 +1719,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131501235</v>
+        <v>131501249</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>80239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387569</v>
+        <v>387577</v>
       </c>
       <c r="R11" t="n">
-        <v>6617686</v>
+        <v>6618050</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1799,6 +1798,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1817,53 +1817,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>80326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R12" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1922,45 +1914,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B13" t="n">
-        <v>80325</v>
+        <v>57896</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R13" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2022,7 +2022,7 @@
         <v>131501247</v>
       </c>
       <c r="B14" t="n">
-        <v>80238</v>
+        <v>80239</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>131501195</v>
       </c>
       <c r="B15" t="n">
-        <v>91791</v>
+        <v>91792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B16" t="n">
-        <v>57086</v>
+        <v>80401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,42 +2225,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R16" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2319,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B17" t="n">
-        <v>80400</v>
+        <v>57087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2322,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R17" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2419,7 +2419,7 @@
         <v>131501227</v>
       </c>
       <c r="B18" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131501229</v>
       </c>
       <c r="B19" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131501228</v>
       </c>
       <c r="B20" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>131501216</v>
       </c>
       <c r="B21" t="n">
-        <v>80269</v>
+        <v>80270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>131501194</v>
       </c>
       <c r="B22" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>131501201</v>
       </c>
       <c r="B23" t="n">
-        <v>80238</v>
+        <v>80239</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501233</v>
+        <v>131501214</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>80270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387666</v>
+        <v>387594</v>
       </c>
       <c r="R24" t="n">
-        <v>6618011</v>
+        <v>6618061</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131501214</v>
+        <v>131501224</v>
       </c>
       <c r="B25" t="n">
-        <v>80269</v>
+        <v>80326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
         <v>387594</v>
       </c>
       <c r="R25" t="n">
-        <v>6618061</v>
+        <v>6617760</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3193,32 +3193,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501224</v>
+        <v>131501233</v>
       </c>
       <c r="B26" t="n">
-        <v>80325</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387594</v>
+        <v>387666</v>
       </c>
       <c r="R26" t="n">
-        <v>6617760</v>
+        <v>6618011</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501239</v>
+        <v>131501242</v>
       </c>
       <c r="B27" t="n">
-        <v>80238</v>
+        <v>80234</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>392</v>
+        <v>6441</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387579</v>
+        <v>387660</v>
       </c>
       <c r="R27" t="n">
-        <v>6618064</v>
+        <v>6617886</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501242</v>
+        <v>131501259</v>
       </c>
       <c r="B28" t="n">
-        <v>80233</v>
+        <v>80401</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6441</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387660</v>
+        <v>387611</v>
       </c>
       <c r="R28" t="n">
-        <v>6617886</v>
+        <v>6617519</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,7 +3467,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3486,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501259</v>
+        <v>131501239</v>
       </c>
       <c r="B29" t="n">
-        <v>80400</v>
+        <v>80239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3521,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387611</v>
+        <v>387579</v>
       </c>
       <c r="R29" t="n">
-        <v>6617519</v>
+        <v>6618064</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3565,6 +3564,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501223</v>
+        <v>131501253</v>
       </c>
       <c r="B30" t="n">
-        <v>83225</v>
+        <v>80401</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>306</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387587</v>
+        <v>387583</v>
       </c>
       <c r="R30" t="n">
-        <v>6617454</v>
+        <v>6618100</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501253</v>
+        <v>131501223</v>
       </c>
       <c r="B31" t="n">
-        <v>80400</v>
+        <v>83226</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387583</v>
+        <v>387587</v>
       </c>
       <c r="R31" t="n">
-        <v>6618100</v>
+        <v>6617454</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3780,7 +3780,7 @@
         <v>131501208</v>
       </c>
       <c r="B32" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>131501204</v>
       </c>
       <c r="B33" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>131501211</v>
       </c>
       <c r="B34" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>131501244</v>
       </c>
       <c r="B35" t="n">
-        <v>80238</v>
+        <v>80239</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>131501246</v>
       </c>
       <c r="B36" t="n">
-        <v>80238</v>
+        <v>80239</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>131501255</v>
       </c>
       <c r="B37" t="n">
-        <v>80400</v>
+        <v>80401</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>131501222</v>
       </c>
       <c r="B38" t="n">
-        <v>92248</v>
+        <v>92249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131501238</v>
+        <v>131501234</v>
       </c>
       <c r="B39" t="n">
-        <v>80238</v>
+        <v>79261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387572</v>
+        <v>387610</v>
       </c>
       <c r="R39" t="n">
-        <v>6618061</v>
+        <v>6617762</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4575,7 +4575,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4597,7 +4596,7 @@
         <v>131501248</v>
       </c>
       <c r="B40" t="n">
-        <v>80238</v>
+        <v>80239</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4692,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131501245</v>
+        <v>131501238</v>
       </c>
       <c r="B41" t="n">
-        <v>80238</v>
+        <v>80239</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4727,10 +4726,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387569</v>
+        <v>387572</v>
       </c>
       <c r="R41" t="n">
-        <v>6617723</v>
+        <v>6618061</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4790,32 +4789,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131501234</v>
+        <v>131501245</v>
       </c>
       <c r="B42" t="n">
-        <v>79260</v>
+        <v>80239</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387610</v>
+        <v>387569</v>
       </c>
       <c r="R42" t="n">
-        <v>6617762</v>
+        <v>6617723</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4869,6 +4868,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501240</v>
+        <v>131501196</v>
       </c>
       <c r="B43" t="n">
-        <v>80238</v>
+        <v>91792</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387597</v>
+        <v>387554</v>
       </c>
       <c r="R43" t="n">
-        <v>6618067</v>
+        <v>6617465</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4966,7 +4966,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4985,45 +4984,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501220</v>
+        <v>131501209</v>
       </c>
       <c r="B44" t="n">
-        <v>92288</v>
+        <v>57896</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387620</v>
+        <v>387543</v>
       </c>
       <c r="R44" t="n">
-        <v>6618075</v>
+        <v>6617571</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5056,6 +5063,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5082,53 +5094,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501209</v>
+        <v>131501220</v>
       </c>
       <c r="B45" t="n">
-        <v>57895</v>
+        <v>92289</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387543</v>
+        <v>387620</v>
       </c>
       <c r="R45" t="n">
-        <v>6617571</v>
+        <v>6618075</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5161,11 +5165,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5192,32 +5191,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501196</v>
+        <v>131501240</v>
       </c>
       <c r="B46" t="n">
-        <v>91791</v>
+        <v>80239</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5226,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387554</v>
+        <v>387597</v>
       </c>
       <c r="R46" t="n">
-        <v>6617465</v>
+        <v>6618067</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5271,6 +5270,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>131501261</v>
       </c>
       <c r="B47" t="n">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>131501212</v>
       </c>
       <c r="B48" t="n">
-        <v>80269</v>
+        <v>80270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>131501252</v>
       </c>
       <c r="B49" t="n">
-        <v>80400</v>
+        <v>80401</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>131501215</v>
       </c>
       <c r="B50" t="n">
-        <v>80269</v>
+        <v>80270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>131501226</v>
       </c>
       <c r="B51" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131501225</v>
       </c>
       <c r="B52" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501263</v>
+        <v>131501218</v>
       </c>
       <c r="B53" t="n">
-        <v>80238</v>
+        <v>80270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387610</v>
+        <v>387575</v>
       </c>
       <c r="R53" t="n">
-        <v>6617561</v>
+        <v>6617729</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5960,7 +5960,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5979,32 +5978,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501218</v>
+        <v>131501236</v>
       </c>
       <c r="B54" t="n">
-        <v>80269</v>
+        <v>79261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6014,10 +6013,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387575</v>
+        <v>387557</v>
       </c>
       <c r="R54" t="n">
-        <v>6617729</v>
+        <v>6617549</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6076,32 +6075,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501236</v>
+        <v>131501263</v>
       </c>
       <c r="B55" t="n">
-        <v>79260</v>
+        <v>80239</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6111,10 +6110,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387557</v>
+        <v>387610</v>
       </c>
       <c r="R55" t="n">
-        <v>6617549</v>
+        <v>6617561</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6155,6 +6154,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>131501210</v>
       </c>
       <c r="B56" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>131501193</v>
       </c>
       <c r="B57" t="n">
-        <v>80238</v>
+        <v>80239</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1430,7 +1430,7 @@
         <v>131501213</v>
       </c>
       <c r="B8" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>131501235</v>
       </c>
       <c r="B9" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131501250</v>
       </c>
       <c r="B10" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>131501249</v>
       </c>
       <c r="B11" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,45 +1817,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B12" t="n">
-        <v>80326</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R12" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1914,53 +1922,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B13" t="n">
-        <v>57896</v>
+        <v>80329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R13" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131501247</v>
+        <v>131501195</v>
       </c>
       <c r="B14" t="n">
-        <v>80239</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387568</v>
+        <v>387619</v>
       </c>
       <c r="R14" t="n">
-        <v>6618040</v>
+        <v>6618073</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2098,7 +2098,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2117,32 +2116,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131501195</v>
+        <v>131501247</v>
       </c>
       <c r="B15" t="n">
-        <v>91792</v>
+        <v>80242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2152,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387619</v>
+        <v>387568</v>
       </c>
       <c r="R15" t="n">
-        <v>6618073</v>
+        <v>6618040</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2196,6 +2195,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>131501257</v>
       </c>
       <c r="B16" t="n">
-        <v>80401</v>
+        <v>80404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131501198</v>
       </c>
       <c r="B17" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>131501227</v>
       </c>
       <c r="B18" t="n">
-        <v>80326</v>
+        <v>80329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131501229</v>
       </c>
       <c r="B19" t="n">
-        <v>80326</v>
+        <v>80329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131501228</v>
       </c>
       <c r="B20" t="n">
-        <v>80326</v>
+        <v>80329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>131501216</v>
       </c>
       <c r="B21" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>131501194</v>
       </c>
       <c r="B22" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>131501201</v>
       </c>
       <c r="B23" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501214</v>
+        <v>131501224</v>
       </c>
       <c r="B24" t="n">
-        <v>80270</v>
+        <v>80329</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3010,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
         <v>387594</v>
       </c>
       <c r="R24" t="n">
-        <v>6618061</v>
+        <v>6617760</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3096,32 +3096,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131501224</v>
+        <v>131501233</v>
       </c>
       <c r="B25" t="n">
-        <v>80326</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387594</v>
+        <v>387666</v>
       </c>
       <c r="R25" t="n">
-        <v>6617760</v>
+        <v>6618011</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3193,32 +3193,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501233</v>
+        <v>131501214</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>80273</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387666</v>
+        <v>387594</v>
       </c>
       <c r="R26" t="n">
-        <v>6618011</v>
+        <v>6618061</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501242</v>
+        <v>131501239</v>
       </c>
       <c r="B27" t="n">
-        <v>80234</v>
+        <v>80242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6441</v>
+        <v>392</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387660</v>
+        <v>387579</v>
       </c>
       <c r="R27" t="n">
-        <v>6617886</v>
+        <v>6618064</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3391,7 +3391,7 @@
         <v>131501259</v>
       </c>
       <c r="B28" t="n">
-        <v>80401</v>
+        <v>80404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501239</v>
+        <v>131501242</v>
       </c>
       <c r="B29" t="n">
-        <v>80239</v>
+        <v>80237</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>6441</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387579</v>
+        <v>387660</v>
       </c>
       <c r="R29" t="n">
-        <v>6618064</v>
+        <v>6617886</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3586,7 +3586,7 @@
         <v>131501253</v>
       </c>
       <c r="B30" t="n">
-        <v>80401</v>
+        <v>80404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,45 +3680,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501223</v>
+        <v>131501211</v>
       </c>
       <c r="B31" t="n">
-        <v>83226</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387587</v>
+        <v>387554</v>
       </c>
       <c r="R31" t="n">
-        <v>6617454</v>
+        <v>6617473</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3780,7 +3788,7 @@
         <v>131501208</v>
       </c>
       <c r="B32" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,7 +3898,7 @@
         <v>131501204</v>
       </c>
       <c r="B33" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3997,53 +4005,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501211</v>
+        <v>131501223</v>
       </c>
       <c r="B34" t="n">
-        <v>57896</v>
+        <v>83229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387554</v>
+        <v>387587</v>
       </c>
       <c r="R34" t="n">
-        <v>6617473</v>
+        <v>6617454</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4105,7 +4105,7 @@
         <v>131501244</v>
       </c>
       <c r="B35" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>131501246</v>
       </c>
       <c r="B36" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4298,45 +4298,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131501255</v>
+        <v>131501222</v>
       </c>
       <c r="B37" t="n">
-        <v>80401</v>
+        <v>92252</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387660</v>
+        <v>387619</v>
       </c>
       <c r="R37" t="n">
-        <v>6617892</v>
+        <v>6618071</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4377,6 +4380,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4395,48 +4399,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131501222</v>
+        <v>131501255</v>
       </c>
       <c r="B38" t="n">
-        <v>92249</v>
+        <v>80404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387619</v>
+        <v>387660</v>
       </c>
       <c r="R38" t="n">
-        <v>6618071</v>
+        <v>6617892</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4477,7 +4478,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131501234</v>
+        <v>131501248</v>
       </c>
       <c r="B39" t="n">
-        <v>79261</v>
+        <v>80242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387610</v>
+        <v>387575</v>
       </c>
       <c r="R39" t="n">
-        <v>6617762</v>
+        <v>6618043</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4575,6 +4575,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4593,10 +4594,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131501248</v>
+        <v>131501238</v>
       </c>
       <c r="B40" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387575</v>
+        <v>387572</v>
       </c>
       <c r="R40" t="n">
-        <v>6618043</v>
+        <v>6618061</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4691,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131501238</v>
+        <v>131501245</v>
       </c>
       <c r="B41" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387572</v>
+        <v>387569</v>
       </c>
       <c r="R41" t="n">
-        <v>6618061</v>
+        <v>6617723</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4789,32 +4790,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131501245</v>
+        <v>131501234</v>
       </c>
       <c r="B42" t="n">
-        <v>80239</v>
+        <v>79264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387569</v>
+        <v>387610</v>
       </c>
       <c r="R42" t="n">
-        <v>6617723</v>
+        <v>6617762</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4868,7 +4869,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501196</v>
+        <v>131501240</v>
       </c>
       <c r="B43" t="n">
-        <v>91792</v>
+        <v>80242</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387554</v>
+        <v>387597</v>
       </c>
       <c r="R43" t="n">
-        <v>6617465</v>
+        <v>6618067</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4966,6 +4966,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4984,53 +4985,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501209</v>
+        <v>131501220</v>
       </c>
       <c r="B44" t="n">
-        <v>57896</v>
+        <v>92292</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387543</v>
+        <v>387620</v>
       </c>
       <c r="R44" t="n">
-        <v>6617571</v>
+        <v>6618075</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5063,11 +5056,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5094,32 +5082,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501220</v>
+        <v>131501196</v>
       </c>
       <c r="B45" t="n">
-        <v>92289</v>
+        <v>91795</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5129,10 +5117,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387620</v>
+        <v>387554</v>
       </c>
       <c r="R45" t="n">
-        <v>6618075</v>
+        <v>6617465</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5191,45 +5179,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501240</v>
+        <v>131501209</v>
       </c>
       <c r="B46" t="n">
-        <v>80239</v>
+        <v>57899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387597</v>
+        <v>387543</v>
       </c>
       <c r="R46" t="n">
-        <v>6618067</v>
+        <v>6617571</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5264,13 +5260,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131501261</v>
+        <v>131501252</v>
       </c>
       <c r="B47" t="n">
-        <v>5178</v>
+        <v>80404</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,43 +5300,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387569</v>
+        <v>387602</v>
       </c>
       <c r="R47" t="n">
-        <v>6617556</v>
+        <v>6618110</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5377,7 +5368,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5396,10 +5386,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131501212</v>
+        <v>131501261</v>
       </c>
       <c r="B48" t="n">
-        <v>80270</v>
+        <v>5178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,34 +5397,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R48" t="n">
-        <v>6618057</v>
+        <v>6617556</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5475,6 +5474,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131501252</v>
+        <v>131501212</v>
       </c>
       <c r="B49" t="n">
-        <v>80401</v>
+        <v>80273</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5504,21 +5504,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387602</v>
+        <v>387577</v>
       </c>
       <c r="R49" t="n">
-        <v>6618110</v>
+        <v>6618057</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5593,7 +5593,7 @@
         <v>131501215</v>
       </c>
       <c r="B50" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>131501226</v>
       </c>
       <c r="B51" t="n">
-        <v>80326</v>
+        <v>80329</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131501225</v>
       </c>
       <c r="B52" t="n">
-        <v>80326</v>
+        <v>80329</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>131501218</v>
       </c>
       <c r="B53" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>131501236</v>
       </c>
       <c r="B54" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>131501263</v>
       </c>
       <c r="B55" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>131501210</v>
       </c>
       <c r="B56" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>131501193</v>
       </c>
       <c r="B57" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6378,6 +6378,2298 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131822720</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>387686</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6617861</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131819716</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91853</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>387662</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6617924</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131816381</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91853</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>387612</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6618032</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Martin Eneling</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Martin Eneling</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131819186</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>387618</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6618030</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131821732</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80329</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Noltomten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>387538</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6617660</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131815937</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80329</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>387618</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6618030</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131822763</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>387686</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6617861</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minst 45 stycks färsk spillning under tall.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131819629</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>387662</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6617924</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131820869</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>387592</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6618084</v>
+      </c>
+      <c r="S66" t="n">
+        <v>7</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Lisa Ingwall-King</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Lisa Ingwall-King</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131820899</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57093</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Noltomten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>387516</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6617582</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131822775</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>387628</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6618089</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Daniel Berger</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Daniel Berger</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131820835</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>387591</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6618103</v>
+      </c>
+      <c r="S69" t="n">
+        <v>18</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Lisa Ingwall-King</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Lisa Ingwall-King</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131820604</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80404</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>387600</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6618141</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Daniel Berger</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Daniel Berger</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131820383</v>
+      </c>
+      <c r="B71" t="n">
+        <v>93158</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Noltomten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>387672</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6617684</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131815985</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>387618</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6618030</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131821338</v>
+      </c>
+      <c r="B73" t="n">
+        <v>75370</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>387631</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6618098</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Daniel Berger</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Daniel Berger</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131817086</v>
+      </c>
+      <c r="B74" t="n">
+        <v>90869</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>889</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Plicatura pendula</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>387612</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6618032</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Martin Eneling</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Martin Eneling</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131821100</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Noltomten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>387541</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6617620</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131816272</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8443</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>387612</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6618060</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131820504</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Noltomten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>387672</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6617684</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501213</v>
+        <v>131501249</v>
       </c>
       <c r="B8" t="n">
-        <v>80273</v>
+        <v>80242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387596</v>
+        <v>387577</v>
       </c>
       <c r="R8" t="n">
-        <v>6618070</v>
+        <v>6618050</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1506,6 +1506,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1524,32 +1525,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501235</v>
+        <v>131501250</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>80242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387569</v>
+        <v>387571</v>
       </c>
       <c r="R9" t="n">
-        <v>6617686</v>
+        <v>6618050</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1603,6 +1604,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1621,32 +1623,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501250</v>
+        <v>131501213</v>
       </c>
       <c r="B10" t="n">
-        <v>80242</v>
+        <v>80273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387571</v>
+        <v>387596</v>
       </c>
       <c r="R10" t="n">
-        <v>6618050</v>
+        <v>6618070</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1700,7 +1702,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1719,32 +1720,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131501249</v>
+        <v>131501235</v>
       </c>
       <c r="B11" t="n">
-        <v>80242</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R11" t="n">
-        <v>6618050</v>
+        <v>6617686</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1798,7 +1799,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131501227</v>
+        <v>131501229</v>
       </c>
       <c r="B18" t="n">
         <v>80329</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387581</v>
+        <v>387557</v>
       </c>
       <c r="R18" t="n">
-        <v>6617713</v>
+        <v>6617663</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131501229</v>
+        <v>131501227</v>
       </c>
       <c r="B19" t="n">
         <v>80329</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387557</v>
+        <v>387581</v>
       </c>
       <c r="R19" t="n">
-        <v>6617663</v>
+        <v>6617713</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501259</v>
+        <v>131501242</v>
       </c>
       <c r="B28" t="n">
-        <v>80404</v>
+        <v>80237</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6441</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387611</v>
+        <v>387660</v>
       </c>
       <c r="R28" t="n">
-        <v>6617519</v>
+        <v>6617886</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,6 +3467,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,10 +3486,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501242</v>
+        <v>131501259</v>
       </c>
       <c r="B29" t="n">
-        <v>80237</v>
+        <v>80404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3496,16 +3497,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6441</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3520,10 +3521,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387660</v>
+        <v>387611</v>
       </c>
       <c r="R29" t="n">
-        <v>6617886</v>
+        <v>6617519</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3564,7 +3565,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3583,45 +3583,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501253</v>
+        <v>131501211</v>
       </c>
       <c r="B30" t="n">
-        <v>80404</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387583</v>
+        <v>387554</v>
       </c>
       <c r="R30" t="n">
-        <v>6618100</v>
+        <v>6617473</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3680,7 +3688,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501211</v>
+        <v>131501204</v>
       </c>
       <c r="B31" t="n">
         <v>57899</v>
@@ -3713,7 +3721,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3723,10 +3731,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387554</v>
+        <v>387618</v>
       </c>
       <c r="R31" t="n">
-        <v>6617473</v>
+        <v>6618118</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3759,6 +3767,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3895,53 +3908,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501204</v>
+        <v>131501223</v>
       </c>
       <c r="B33" t="n">
-        <v>57899</v>
+        <v>83229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387618</v>
+        <v>387587</v>
       </c>
       <c r="R33" t="n">
-        <v>6618118</v>
+        <v>6617454</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3974,11 +3979,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4005,10 +4005,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501223</v>
+        <v>131501253</v>
       </c>
       <c r="B34" t="n">
-        <v>83229</v>
+        <v>80404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,21 +4016,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>306</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387587</v>
+        <v>387583</v>
       </c>
       <c r="R34" t="n">
-        <v>6617454</v>
+        <v>6618100</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4298,48 +4298,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131501222</v>
+        <v>131501255</v>
       </c>
       <c r="B37" t="n">
-        <v>92252</v>
+        <v>80404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387619</v>
+        <v>387660</v>
       </c>
       <c r="R37" t="n">
-        <v>6618071</v>
+        <v>6617892</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4380,7 +4377,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4399,45 +4395,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131501255</v>
+        <v>131501222</v>
       </c>
       <c r="B38" t="n">
-        <v>80404</v>
+        <v>92252</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6040186</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387660</v>
+        <v>387619</v>
       </c>
       <c r="R38" t="n">
-        <v>6617892</v>
+        <v>6618071</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4478,6 +4477,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131501248</v>
+        <v>131501234</v>
       </c>
       <c r="B39" t="n">
-        <v>80242</v>
+        <v>79264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387575</v>
+        <v>387610</v>
       </c>
       <c r="R39" t="n">
-        <v>6618043</v>
+        <v>6617762</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4575,7 +4575,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4692,7 +4691,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131501245</v>
+        <v>131501248</v>
       </c>
       <c r="B41" t="n">
         <v>80242</v>
@@ -4727,10 +4726,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387569</v>
+        <v>387575</v>
       </c>
       <c r="R41" t="n">
-        <v>6617723</v>
+        <v>6618043</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4790,32 +4789,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131501234</v>
+        <v>131501245</v>
       </c>
       <c r="B42" t="n">
-        <v>79264</v>
+        <v>80242</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387610</v>
+        <v>387569</v>
       </c>
       <c r="R42" t="n">
-        <v>6617762</v>
+        <v>6617723</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4869,6 +4868,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5082,45 +5082,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501196</v>
+        <v>131501209</v>
       </c>
       <c r="B45" t="n">
-        <v>91795</v>
+        <v>57899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387554</v>
+        <v>387543</v>
       </c>
       <c r="R45" t="n">
-        <v>6617465</v>
+        <v>6617571</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5153,6 +5161,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5179,53 +5192,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501209</v>
+        <v>131501196</v>
       </c>
       <c r="B46" t="n">
-        <v>57899</v>
+        <v>91795</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387543</v>
+        <v>387554</v>
       </c>
       <c r="R46" t="n">
-        <v>6617571</v>
+        <v>6617465</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5258,11 +5263,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131501252</v>
+        <v>131501212</v>
       </c>
       <c r="B47" t="n">
-        <v>80404</v>
+        <v>80273</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,21 +5300,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387602</v>
+        <v>387577</v>
       </c>
       <c r="R47" t="n">
-        <v>6618110</v>
+        <v>6618057</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131501261</v>
+        <v>131501252</v>
       </c>
       <c r="B48" t="n">
-        <v>5178</v>
+        <v>80404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5397,43 +5397,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387569</v>
+        <v>387602</v>
       </c>
       <c r="R48" t="n">
-        <v>6617556</v>
+        <v>6618110</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5474,7 +5465,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5493,10 +5483,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131501212</v>
+        <v>131501261</v>
       </c>
       <c r="B49" t="n">
-        <v>80273</v>
+        <v>5178</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5504,34 +5494,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R49" t="n">
-        <v>6618057</v>
+        <v>6617556</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5572,6 +5571,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501218</v>
+        <v>131501263</v>
       </c>
       <c r="B53" t="n">
-        <v>80273</v>
+        <v>80242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387575</v>
+        <v>387610</v>
       </c>
       <c r="R53" t="n">
-        <v>6617729</v>
+        <v>6617561</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5960,6 +5960,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5978,32 +5979,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501236</v>
+        <v>131501218</v>
       </c>
       <c r="B54" t="n">
-        <v>79264</v>
+        <v>80273</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6013,10 +6014,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387557</v>
+        <v>387575</v>
       </c>
       <c r="R54" t="n">
-        <v>6617549</v>
+        <v>6617729</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6075,32 +6076,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501263</v>
+        <v>131501236</v>
       </c>
       <c r="B55" t="n">
-        <v>80242</v>
+        <v>79264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6110,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387610</v>
+        <v>387557</v>
       </c>
       <c r="R55" t="n">
-        <v>6617561</v>
+        <v>6617549</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6154,7 +6155,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131822720</v>
+        <v>131819716</v>
       </c>
       <c r="B58" t="n">
-        <v>57899</v>
+        <v>91853</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6416,12 +6416,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6430,10 +6425,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>387686</v>
+        <v>387662</v>
       </c>
       <c r="R58" t="n">
-        <v>6617861</v>
+        <v>6617924</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6465,7 +6460,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6475,7 +6470,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6502,10 +6497,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131819716</v>
+        <v>131822720</v>
       </c>
       <c r="B59" t="n">
-        <v>91853</v>
+        <v>57899</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,21 +6508,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6537,7 +6532,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387662</v>
+        <v>387686</v>
       </c>
       <c r="R59" t="n">
-        <v>6617924</v>
+        <v>6617861</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6736,10 +6736,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131819186</v>
+        <v>131821732</v>
       </c>
       <c r="B61" t="n">
-        <v>57090</v>
+        <v>80329</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6747,53 +6747,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>387618</v>
+        <v>387538</v>
       </c>
       <c r="R61" t="n">
-        <v>6618030</v>
+        <v>6617660</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,7 +6806,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6835,12 +6816,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6867,10 +6843,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131821732</v>
+        <v>131819186</v>
       </c>
       <c r="B62" t="n">
-        <v>80329</v>
+        <v>57090</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,34 +6854,53 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387538</v>
+        <v>387618</v>
       </c>
       <c r="R62" t="n">
-        <v>6617660</v>
+        <v>6618030</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6937,7 +6932,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6947,7 +6942,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7207,67 +7207,57 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131819629</v>
+        <v>131820869</v>
       </c>
       <c r="B65" t="n">
-        <v>57090</v>
+        <v>99038</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>387662</v>
+        <v>387592</v>
       </c>
       <c r="R65" t="n">
-        <v>6617924</v>
+        <v>6618084</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7294,24 +7284,9 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7326,69 +7301,79 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131820869</v>
+        <v>131819629</v>
       </c>
       <c r="B66" t="n">
-        <v>99038</v>
+        <v>57090</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387592</v>
+        <v>387662</v>
       </c>
       <c r="R66" t="n">
-        <v>6618084</v>
+        <v>6617924</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7415,9 +7400,24 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7432,12 +7432,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131815985</v>
+        <v>131821338</v>
       </c>
       <c r="B72" t="n">
-        <v>80398</v>
+        <v>75370</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8003,37 +8003,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387618</v>
+        <v>387631</v>
       </c>
       <c r="R72" t="n">
-        <v>6618030</v>
+        <v>6618098</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8087,22 +8087,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131821338</v>
+        <v>131815985</v>
       </c>
       <c r="B73" t="n">
-        <v>75370</v>
+        <v>80398</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8110,37 +8110,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387631</v>
+        <v>387618</v>
       </c>
       <c r="R73" t="n">
-        <v>6618098</v>
+        <v>6618030</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8194,12 +8194,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131816272</v>
+        <v>131820504</v>
       </c>
       <c r="B76" t="n">
-        <v>8443</v>
+        <v>91795</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8456,48 +8456,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387612</v>
+        <v>387672</v>
       </c>
       <c r="R76" t="n">
-        <v>6618060</v>
+        <v>6617684</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,7 +8515,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8539,7 +8525,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8566,10 +8552,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131820504</v>
+        <v>131816272</v>
       </c>
       <c r="B77" t="n">
-        <v>91795</v>
+        <v>8443</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8577,34 +8563,48 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387672</v>
+        <v>387612</v>
       </c>
       <c r="R77" t="n">
-        <v>6617684</v>
+        <v>6618060</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8670,6 +8670,678 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131816249</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>387608</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6618019</v>
+      </c>
+      <c r="S78" t="n">
+        <v>6</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>131823453</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>387667</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6617721</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131821057</v>
+      </c>
+      <c r="B80" t="n">
+        <v>4774</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>387610</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6618114</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131820532</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>387623</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6618155</v>
+      </c>
+      <c r="S81" t="n">
+        <v>6</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>6 blomställningar från förra året</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>131821233</v>
+      </c>
+      <c r="B82" t="n">
+        <v>5198</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>387621</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6618115</v>
+      </c>
+      <c r="S82" t="n">
+        <v>8</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>131820813</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80404</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>387611</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6618100</v>
+      </c>
+      <c r="S83" t="n">
+        <v>8</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501249</v>
+        <v>131501213</v>
       </c>
       <c r="B8" t="n">
-        <v>80242</v>
+        <v>80273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387577</v>
+        <v>387596</v>
       </c>
       <c r="R8" t="n">
-        <v>6618050</v>
+        <v>6618070</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1506,19 +1506,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1611,44 +1610,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501213</v>
+        <v>131501249</v>
       </c>
       <c r="B10" t="n">
-        <v>80273</v>
+        <v>80242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1658,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387596</v>
+        <v>387577</v>
       </c>
       <c r="R10" t="n">
-        <v>6618070</v>
+        <v>6618050</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1702,18 +1701,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1805,12 +1805,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1910,12 +1910,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2007,44 +2007,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131501195</v>
+        <v>131501247</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>80242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387619</v>
+        <v>387568</v>
       </c>
       <c r="R14" t="n">
-        <v>6618073</v>
+        <v>6618040</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2098,50 +2098,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131501247</v>
+        <v>131501195</v>
       </c>
       <c r="B15" t="n">
-        <v>80242</v>
+        <v>91795</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387568</v>
+        <v>387619</v>
       </c>
       <c r="R15" t="n">
-        <v>6618040</v>
+        <v>6618073</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2195,29 +2196,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B16" t="n">
-        <v>80404</v>
+        <v>57090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,34 +2225,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R16" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2299,22 +2307,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B17" t="n">
-        <v>57090</v>
+        <v>80404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,42 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R17" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2404,19 +2404,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131501229</v>
+        <v>131501227</v>
       </c>
       <c r="B18" t="n">
         <v>80329</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387557</v>
+        <v>387581</v>
       </c>
       <c r="R18" t="n">
-        <v>6617663</v>
+        <v>6617713</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2501,19 +2501,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131501227</v>
+        <v>131501229</v>
       </c>
       <c r="B19" t="n">
         <v>80329</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387581</v>
+        <v>387557</v>
       </c>
       <c r="R19" t="n">
-        <v>6617713</v>
+        <v>6617663</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2598,12 +2598,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2695,44 +2695,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131501216</v>
+        <v>131501194</v>
       </c>
       <c r="B21" t="n">
-        <v>80273</v>
+        <v>83244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387664</v>
+        <v>387560</v>
       </c>
       <c r="R21" t="n">
-        <v>6617891</v>
+        <v>6617541</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2792,44 +2792,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131501194</v>
+        <v>131501216</v>
       </c>
       <c r="B22" t="n">
-        <v>83244</v>
+        <v>80273</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387560</v>
+        <v>387664</v>
       </c>
       <c r="R22" t="n">
-        <v>6617541</v>
+        <v>6617891</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2889,12 +2889,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2987,44 +2987,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501224</v>
+        <v>131501233</v>
       </c>
       <c r="B24" t="n">
-        <v>80329</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387594</v>
+        <v>387666</v>
       </c>
       <c r="R24" t="n">
-        <v>6617760</v>
+        <v>6618011</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3084,44 +3084,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131501233</v>
+        <v>131501214</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>80273</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387666</v>
+        <v>387594</v>
       </c>
       <c r="R25" t="n">
-        <v>6618011</v>
+        <v>6618061</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3181,22 +3181,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501214</v>
+        <v>131501224</v>
       </c>
       <c r="B26" t="n">
-        <v>80273</v>
+        <v>80329</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
         <v>387594</v>
       </c>
       <c r="R26" t="n">
-        <v>6618061</v>
+        <v>6617760</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3278,12 +3278,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3376,12 +3376,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3474,12 +3474,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3571,65 +3571,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501211</v>
+        <v>131501253</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>80404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387554</v>
+        <v>387583</v>
       </c>
       <c r="R30" t="n">
-        <v>6617473</v>
+        <v>6618100</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3676,19 +3668,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501204</v>
+        <v>131501208</v>
       </c>
       <c r="B31" t="n">
         <v>57899</v>
@@ -3731,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387618</v>
+        <v>387565</v>
       </c>
       <c r="R31" t="n">
-        <v>6618118</v>
+        <v>6617589</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3786,19 +3778,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501208</v>
+        <v>131501204</v>
       </c>
       <c r="B32" t="n">
         <v>57899</v>
@@ -3841,10 +3833,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387565</v>
+        <v>387618</v>
       </c>
       <c r="R32" t="n">
-        <v>6617589</v>
+        <v>6618118</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3896,57 +3888,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501223</v>
+        <v>131501211</v>
       </c>
       <c r="B33" t="n">
-        <v>83229</v>
+        <v>57899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387587</v>
+        <v>387554</v>
       </c>
       <c r="R33" t="n">
-        <v>6617454</v>
+        <v>6617473</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3993,22 +3993,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501253</v>
+        <v>131501223</v>
       </c>
       <c r="B34" t="n">
-        <v>80404</v>
+        <v>83229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,21 +4016,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387583</v>
+        <v>387587</v>
       </c>
       <c r="R34" t="n">
-        <v>6618100</v>
+        <v>6617454</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4090,12 +4090,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4188,12 +4188,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4286,12 +4286,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4383,12 +4383,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4484,44 +4484,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131501234</v>
+        <v>131501248</v>
       </c>
       <c r="B39" t="n">
-        <v>79264</v>
+        <v>80242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387610</v>
+        <v>387575</v>
       </c>
       <c r="R39" t="n">
-        <v>6617762</v>
+        <v>6618043</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4575,18 +4575,19 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4679,19 +4680,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131501248</v>
+        <v>131501245</v>
       </c>
       <c r="B41" t="n">
         <v>80242</v>
@@ -4726,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387575</v>
+        <v>387569</v>
       </c>
       <c r="R41" t="n">
-        <v>6618043</v>
+        <v>6617723</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4777,44 +4778,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131501245</v>
+        <v>131501234</v>
       </c>
       <c r="B42" t="n">
-        <v>80242</v>
+        <v>79264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387569</v>
+        <v>387610</v>
       </c>
       <c r="R42" t="n">
-        <v>6617723</v>
+        <v>6617762</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4868,19 +4869,18 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4973,12 +4973,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5070,65 +5070,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501209</v>
+        <v>131501196</v>
       </c>
       <c r="B45" t="n">
-        <v>57899</v>
+        <v>91795</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387543</v>
+        <v>387554</v>
       </c>
       <c r="R45" t="n">
-        <v>6617571</v>
+        <v>6617465</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5163,11 +5155,6 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5180,57 +5167,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501196</v>
+        <v>131501209</v>
       </c>
       <c r="B46" t="n">
-        <v>91795</v>
+        <v>57899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387554</v>
+        <v>387543</v>
       </c>
       <c r="R46" t="n">
-        <v>6617465</v>
+        <v>6617571</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5265,6 +5260,11 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5277,12 +5277,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5374,12 +5374,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5471,12 +5471,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5578,12 +5578,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5675,12 +5675,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5772,12 +5772,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5869,12 +5869,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5967,44 +5967,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501218</v>
+        <v>131501236</v>
       </c>
       <c r="B54" t="n">
-        <v>80273</v>
+        <v>79264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387575</v>
+        <v>387557</v>
       </c>
       <c r="R54" t="n">
-        <v>6617729</v>
+        <v>6617549</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6064,44 +6064,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501236</v>
+        <v>131501218</v>
       </c>
       <c r="B55" t="n">
-        <v>79264</v>
+        <v>80273</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387557</v>
+        <v>387575</v>
       </c>
       <c r="R55" t="n">
-        <v>6617549</v>
+        <v>6617729</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6161,12 +6161,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6271,12 +6271,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6369,12 +6369,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131821732</v>
+        <v>131819186</v>
       </c>
       <c r="B61" t="n">
-        <v>80329</v>
+        <v>57090</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6747,34 +6747,53 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>387538</v>
+        <v>387618</v>
       </c>
       <c r="R61" t="n">
-        <v>6617660</v>
+        <v>6618030</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6806,7 +6825,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6816,7 +6835,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6843,10 +6867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131819186</v>
+        <v>131821732</v>
       </c>
       <c r="B62" t="n">
-        <v>57090</v>
+        <v>80329</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6854,53 +6878,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387618</v>
+        <v>387538</v>
       </c>
       <c r="R62" t="n">
-        <v>6618030</v>
+        <v>6617660</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6937,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6942,12 +6947,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7207,57 +7207,67 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131820869</v>
+        <v>131819629</v>
       </c>
       <c r="B65" t="n">
-        <v>99038</v>
+        <v>57090</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>387592</v>
+        <v>387662</v>
       </c>
       <c r="R65" t="n">
-        <v>6618084</v>
+        <v>6617924</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7284,9 +7294,24 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7301,79 +7326,69 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131819629</v>
+        <v>131820869</v>
       </c>
       <c r="B66" t="n">
-        <v>57090</v>
+        <v>99038</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387662</v>
+        <v>387592</v>
       </c>
       <c r="R66" t="n">
-        <v>6617924</v>
+        <v>6618084</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7400,24 +7415,9 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7432,69 +7432,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B67" t="n">
-        <v>57093</v>
+        <v>92292</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R67" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7523,7 +7514,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7533,12 +7524,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,60 +7539,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B68" t="n">
-        <v>92292</v>
+        <v>57093</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R68" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7635,7 +7630,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7645,7 +7640,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8206,59 +8206,62 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131817086</v>
+        <v>131821100</v>
       </c>
       <c r="B74" t="n">
-        <v>90869</v>
+        <v>99038</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>889</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387612</v>
+        <v>387541</v>
       </c>
       <c r="R74" t="n">
-        <v>6618032</v>
+        <v>6617620</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8287,7 +8290,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8297,7 +8300,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8312,74 +8315,71 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131821100</v>
+        <v>131817086</v>
       </c>
       <c r="B75" t="n">
-        <v>99038</v>
+        <v>90869</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>889</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387541</v>
+        <v>387612</v>
       </c>
       <c r="R75" t="n">
-        <v>6617620</v>
+        <v>6618032</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8433,12 +8433,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501213</v>
+        <v>131501235</v>
       </c>
       <c r="B8" t="n">
-        <v>80273</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387596</v>
+        <v>387569</v>
       </c>
       <c r="R8" t="n">
-        <v>6618070</v>
+        <v>6617686</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1524,32 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501250</v>
+        <v>131501213</v>
       </c>
       <c r="B9" t="n">
-        <v>80242</v>
+        <v>80273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387571</v>
+        <v>387596</v>
       </c>
       <c r="R9" t="n">
-        <v>6618050</v>
+        <v>6618070</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1603,7 +1603,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1622,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501249</v>
+        <v>131501250</v>
       </c>
       <c r="B10" t="n">
         <v>80242</v>
@@ -1657,7 +1656,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387577</v>
+        <v>387571</v>
       </c>
       <c r="R10" t="n">
         <v>6618050</v>
@@ -1720,32 +1719,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131501235</v>
+        <v>131501249</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>80242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387569</v>
+        <v>387577</v>
       </c>
       <c r="R11" t="n">
-        <v>6617686</v>
+        <v>6618050</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1799,6 +1798,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501253</v>
+        <v>131501223</v>
       </c>
       <c r="B30" t="n">
-        <v>80404</v>
+        <v>83229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387583</v>
+        <v>387587</v>
       </c>
       <c r="R30" t="n">
-        <v>6618100</v>
+        <v>6617454</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3680,53 +3680,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501208</v>
+        <v>131501253</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>80404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387565</v>
+        <v>387583</v>
       </c>
       <c r="R31" t="n">
-        <v>6617589</v>
+        <v>6618100</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3759,11 +3751,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3790,7 +3777,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501204</v>
+        <v>131501208</v>
       </c>
       <c r="B32" t="n">
         <v>57899</v>
@@ -3833,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387618</v>
+        <v>387565</v>
       </c>
       <c r="R32" t="n">
-        <v>6618118</v>
+        <v>6617589</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3900,7 +3887,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501211</v>
+        <v>131501204</v>
       </c>
       <c r="B33" t="n">
         <v>57899</v>
@@ -3933,7 +3920,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3943,10 +3930,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387554</v>
+        <v>387618</v>
       </c>
       <c r="R33" t="n">
-        <v>6617473</v>
+        <v>6618118</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3979,6 +3966,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4005,45 +3997,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501223</v>
+        <v>131501211</v>
       </c>
       <c r="B34" t="n">
-        <v>83229</v>
+        <v>57899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387587</v>
+        <v>387554</v>
       </c>
       <c r="R34" t="n">
-        <v>6617454</v>
+        <v>6617473</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501235</v>
+        <v>131501213</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>80275</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387569</v>
+        <v>387596</v>
       </c>
       <c r="R8" t="n">
-        <v>6617686</v>
+        <v>6618070</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1524,32 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501213</v>
+        <v>131501235</v>
       </c>
       <c r="B9" t="n">
-        <v>80273</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387596</v>
+        <v>387569</v>
       </c>
       <c r="R9" t="n">
-        <v>6618070</v>
+        <v>6617686</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1624,7 +1624,7 @@
         <v>131501250</v>
       </c>
       <c r="B10" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>131501249</v>
       </c>
       <c r="B11" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>131501203</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>131501230</v>
       </c>
       <c r="B13" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>131501247</v>
       </c>
       <c r="B14" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>131501195</v>
       </c>
       <c r="B15" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B16" t="n">
-        <v>57090</v>
+        <v>80406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,42 +2225,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R16" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2319,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B17" t="n">
-        <v>80404</v>
+        <v>57092</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2322,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R17" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2419,7 +2419,7 @@
         <v>131501227</v>
       </c>
       <c r="B18" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131501229</v>
       </c>
       <c r="B19" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131501228</v>
       </c>
       <c r="B20" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,32 +2707,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131501194</v>
+        <v>131501216</v>
       </c>
       <c r="B21" t="n">
-        <v>83244</v>
+        <v>80275</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387560</v>
+        <v>387664</v>
       </c>
       <c r="R21" t="n">
-        <v>6617541</v>
+        <v>6617891</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2804,32 +2804,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131501216</v>
+        <v>131501194</v>
       </c>
       <c r="B22" t="n">
-        <v>80273</v>
+        <v>83246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387664</v>
+        <v>387560</v>
       </c>
       <c r="R22" t="n">
-        <v>6617891</v>
+        <v>6617541</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2904,7 +2904,7 @@
         <v>131501201</v>
       </c>
       <c r="B23" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501233</v>
+        <v>131501224</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>80331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387666</v>
+        <v>387594</v>
       </c>
       <c r="R24" t="n">
-        <v>6618011</v>
+        <v>6617760</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3099,7 +3099,7 @@
         <v>131501214</v>
       </c>
       <c r="B25" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3193,32 +3193,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501224</v>
+        <v>131501233</v>
       </c>
       <c r="B26" t="n">
-        <v>80329</v>
+        <v>79266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387594</v>
+        <v>387666</v>
       </c>
       <c r="R26" t="n">
-        <v>6617760</v>
+        <v>6618011</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501239</v>
+        <v>131501259</v>
       </c>
       <c r="B27" t="n">
-        <v>80242</v>
+        <v>80406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387579</v>
+        <v>387611</v>
       </c>
       <c r="R27" t="n">
-        <v>6618064</v>
+        <v>6617519</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3369,7 +3369,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3391,7 +3390,7 @@
         <v>131501242</v>
       </c>
       <c r="B28" t="n">
-        <v>80237</v>
+        <v>80239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3486,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501259</v>
+        <v>131501239</v>
       </c>
       <c r="B29" t="n">
-        <v>80404</v>
+        <v>80244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3521,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387611</v>
+        <v>387579</v>
       </c>
       <c r="R29" t="n">
-        <v>6617519</v>
+        <v>6618064</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3565,6 +3564,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501223</v>
+        <v>131501253</v>
       </c>
       <c r="B30" t="n">
-        <v>83229</v>
+        <v>80406</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>306</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387587</v>
+        <v>387583</v>
       </c>
       <c r="R30" t="n">
-        <v>6617454</v>
+        <v>6618100</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3680,45 +3680,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501253</v>
+        <v>131501208</v>
       </c>
       <c r="B31" t="n">
-        <v>80404</v>
+        <v>57901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387583</v>
+        <v>387565</v>
       </c>
       <c r="R31" t="n">
-        <v>6618100</v>
+        <v>6617589</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3751,6 +3759,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3777,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501208</v>
+        <v>131501204</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3820,10 +3833,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387565</v>
+        <v>387618</v>
       </c>
       <c r="R32" t="n">
-        <v>6617589</v>
+        <v>6618118</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3887,10 +3900,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501204</v>
+        <v>131501211</v>
       </c>
       <c r="B33" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3920,7 +3933,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3930,10 +3943,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387618</v>
+        <v>387554</v>
       </c>
       <c r="R33" t="n">
-        <v>6618118</v>
+        <v>6617473</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3966,11 +3979,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3997,53 +4005,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501211</v>
+        <v>131501223</v>
       </c>
       <c r="B34" t="n">
-        <v>57899</v>
+        <v>83231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387554</v>
+        <v>387587</v>
       </c>
       <c r="R34" t="n">
-        <v>6617473</v>
+        <v>6617454</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4105,7 +4105,7 @@
         <v>131501244</v>
       </c>
       <c r="B35" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>131501246</v>
       </c>
       <c r="B36" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>131501255</v>
       </c>
       <c r="B37" t="n">
-        <v>80404</v>
+        <v>80406</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>131501222</v>
       </c>
       <c r="B38" t="n">
-        <v>92252</v>
+        <v>92258</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>131501248</v>
       </c>
       <c r="B39" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>131501238</v>
       </c>
       <c r="B40" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>131501245</v>
       </c>
       <c r="B41" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>131501234</v>
       </c>
       <c r="B42" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>131501240</v>
       </c>
       <c r="B43" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>131501220</v>
       </c>
       <c r="B44" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>131501196</v>
       </c>
       <c r="B45" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>131501209</v>
       </c>
       <c r="B46" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>131501212</v>
       </c>
       <c r="B47" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131501252</v>
       </c>
       <c r="B48" t="n">
-        <v>80404</v>
+        <v>80406</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>131501215</v>
       </c>
       <c r="B50" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>131501226</v>
       </c>
       <c r="B51" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131501225</v>
       </c>
       <c r="B52" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>131501263</v>
       </c>
       <c r="B53" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501236</v>
+        <v>131501210</v>
       </c>
       <c r="B54" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5990,34 +5990,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387557</v>
+        <v>387596</v>
       </c>
       <c r="R54" t="n">
-        <v>6617549</v>
+        <v>6617548</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6050,6 +6058,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6079,7 +6092,7 @@
         <v>131501218</v>
       </c>
       <c r="B55" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6173,10 +6186,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501210</v>
+        <v>131501236</v>
       </c>
       <c r="B56" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6184,42 +6197,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387596</v>
+        <v>387557</v>
       </c>
       <c r="R56" t="n">
-        <v>6617548</v>
+        <v>6617549</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6252,11 +6257,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6286,7 +6286,7 @@
         <v>131501193</v>
       </c>
       <c r="B57" t="n">
-        <v>80242</v>
+        <v>80244</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131819716</v>
+        <v>131822720</v>
       </c>
       <c r="B58" t="n">
-        <v>91853</v>
+        <v>57901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6416,7 +6416,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6425,10 +6430,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>387662</v>
+        <v>387686</v>
       </c>
       <c r="R58" t="n">
-        <v>6617924</v>
+        <v>6617861</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6460,7 +6465,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6470,7 +6475,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6497,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131822720</v>
+        <v>131819716</v>
       </c>
       <c r="B59" t="n">
-        <v>57899</v>
+        <v>91859</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6508,21 +6513,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6532,12 +6537,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387686</v>
+        <v>387662</v>
       </c>
       <c r="R59" t="n">
-        <v>6617861</v>
+        <v>6617924</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6621,7 +6621,7 @@
         <v>131816381</v>
       </c>
       <c r="B60" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>131819186</v>
       </c>
       <c r="B61" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>131821732</v>
       </c>
       <c r="B62" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>131815937</v>
       </c>
       <c r="B63" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>131822763</v>
       </c>
       <c r="B64" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>131819629</v>
       </c>
       <c r="B65" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>131820869</v>
       </c>
       <c r="B66" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>131822775</v>
       </c>
       <c r="B67" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>131820899</v>
       </c>
       <c r="B68" t="n">
-        <v>57093</v>
+        <v>57095</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>131820835</v>
       </c>
       <c r="B69" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>131820604</v>
       </c>
       <c r="B70" t="n">
-        <v>80404</v>
+        <v>80406</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7885,45 +7885,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131820383</v>
+        <v>131815985</v>
       </c>
       <c r="B71" t="n">
-        <v>93158</v>
+        <v>80400</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387672</v>
+        <v>387618</v>
       </c>
       <c r="R71" t="n">
-        <v>6617684</v>
+        <v>6618030</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7995,7 +7995,7 @@
         <v>131821338</v>
       </c>
       <c r="B72" t="n">
-        <v>75370</v>
+        <v>75372</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8099,45 +8099,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131815985</v>
+        <v>131820383</v>
       </c>
       <c r="B73" t="n">
-        <v>80398</v>
+        <v>93164</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387618</v>
+        <v>387672</v>
       </c>
       <c r="R73" t="n">
-        <v>6618030</v>
+        <v>6617684</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8209,7 +8209,7 @@
         <v>131821100</v>
       </c>
       <c r="B74" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>131817086</v>
       </c>
       <c r="B75" t="n">
-        <v>90869</v>
+        <v>90875</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>131820504</v>
       </c>
       <c r="B76" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>131816249</v>
       </c>
       <c r="B78" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>131823453</v>
       </c>
       <c r="B79" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>131820532</v>
       </c>
       <c r="B81" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>131820813</v>
       </c>
       <c r="B83" t="n">
-        <v>80404</v>
+        <v>80406</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501213</v>
+        <v>131501250</v>
       </c>
       <c r="B8" t="n">
-        <v>80275</v>
+        <v>80244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387596</v>
+        <v>387571</v>
       </c>
       <c r="R8" t="n">
-        <v>6618070</v>
+        <v>6618050</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1506,6 +1506,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1524,32 +1525,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501235</v>
+        <v>131501249</v>
       </c>
       <c r="B9" t="n">
-        <v>79266</v>
+        <v>80244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387569</v>
+        <v>387577</v>
       </c>
       <c r="R9" t="n">
-        <v>6617686</v>
+        <v>6618050</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1603,6 +1604,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1621,32 +1623,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501250</v>
+        <v>131501213</v>
       </c>
       <c r="B10" t="n">
-        <v>80244</v>
+        <v>80275</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387571</v>
+        <v>387596</v>
       </c>
       <c r="R10" t="n">
-        <v>6618050</v>
+        <v>6618070</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1700,7 +1702,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1719,32 +1720,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131501249</v>
+        <v>131501235</v>
       </c>
       <c r="B11" t="n">
-        <v>80244</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R11" t="n">
-        <v>6618050</v>
+        <v>6617686</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1798,7 +1799,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1817,53 +1817,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B12" t="n">
-        <v>57901</v>
+        <v>80331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R12" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1922,45 +1914,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B13" t="n">
-        <v>80331</v>
+        <v>57901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R13" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B16" t="n">
-        <v>80406</v>
+        <v>57092</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,34 +2225,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R16" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2311,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B17" t="n">
-        <v>57092</v>
+        <v>80406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,42 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R17" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501224</v>
+        <v>131501214</v>
       </c>
       <c r="B24" t="n">
-        <v>80331</v>
+        <v>80275</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3010,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
         <v>387594</v>
       </c>
       <c r="R24" t="n">
-        <v>6617760</v>
+        <v>6618061</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3096,32 +3096,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131501214</v>
+        <v>131501233</v>
       </c>
       <c r="B25" t="n">
-        <v>80275</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387594</v>
+        <v>387666</v>
       </c>
       <c r="R25" t="n">
-        <v>6618061</v>
+        <v>6618011</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3193,32 +3193,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501233</v>
+        <v>131501224</v>
       </c>
       <c r="B26" t="n">
-        <v>79266</v>
+        <v>80331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387666</v>
+        <v>387594</v>
       </c>
       <c r="R26" t="n">
-        <v>6618011</v>
+        <v>6617760</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3680,53 +3680,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501208</v>
+        <v>131501223</v>
       </c>
       <c r="B31" t="n">
-        <v>57901</v>
+        <v>83231</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387565</v>
+        <v>387587</v>
       </c>
       <c r="R31" t="n">
-        <v>6617589</v>
+        <v>6617454</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3759,11 +3751,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3790,7 +3777,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501204</v>
+        <v>131501208</v>
       </c>
       <c r="B32" t="n">
         <v>57901</v>
@@ -3833,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387618</v>
+        <v>387565</v>
       </c>
       <c r="R32" t="n">
-        <v>6618118</v>
+        <v>6617589</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3900,7 +3887,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501211</v>
+        <v>131501204</v>
       </c>
       <c r="B33" t="n">
         <v>57901</v>
@@ -3933,7 +3920,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3943,10 +3930,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387554</v>
+        <v>387618</v>
       </c>
       <c r="R33" t="n">
-        <v>6617473</v>
+        <v>6618118</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3979,6 +3966,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4005,45 +3997,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501223</v>
+        <v>131501211</v>
       </c>
       <c r="B34" t="n">
-        <v>83231</v>
+        <v>57901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387587</v>
+        <v>387554</v>
       </c>
       <c r="R34" t="n">
-        <v>6617454</v>
+        <v>6617473</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4887,45 +4887,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501240</v>
+        <v>131501209</v>
       </c>
       <c r="B43" t="n">
-        <v>80244</v>
+        <v>57901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387597</v>
+        <v>387543</v>
       </c>
       <c r="R43" t="n">
-        <v>6618067</v>
+        <v>6617571</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4960,13 +4968,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4985,10 +4997,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501220</v>
+        <v>131501240</v>
       </c>
       <c r="B44" t="n">
-        <v>92298</v>
+        <v>80244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4996,21 +5008,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>392</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5020,10 +5032,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387620</v>
+        <v>387597</v>
       </c>
       <c r="R44" t="n">
-        <v>6618075</v>
+        <v>6618067</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5064,6 +5076,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5082,32 +5095,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501196</v>
+        <v>131501220</v>
       </c>
       <c r="B45" t="n">
-        <v>91801</v>
+        <v>92298</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5117,10 +5130,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387554</v>
+        <v>387620</v>
       </c>
       <c r="R45" t="n">
-        <v>6617465</v>
+        <v>6618075</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5179,53 +5192,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501209</v>
+        <v>131501196</v>
       </c>
       <c r="B46" t="n">
-        <v>57901</v>
+        <v>91801</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387543</v>
+        <v>387554</v>
       </c>
       <c r="R46" t="n">
-        <v>6617571</v>
+        <v>6617465</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5258,11 +5263,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501259</v>
+        <v>131501239</v>
       </c>
       <c r="B27" t="n">
-        <v>80406</v>
+        <v>80244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387611</v>
+        <v>387579</v>
       </c>
       <c r="R27" t="n">
-        <v>6617519</v>
+        <v>6618064</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3369,6 +3369,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3387,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501242</v>
+        <v>131501259</v>
       </c>
       <c r="B28" t="n">
-        <v>80239</v>
+        <v>80406</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6441</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3422,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387660</v>
+        <v>387611</v>
       </c>
       <c r="R28" t="n">
-        <v>6617886</v>
+        <v>6617519</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3466,7 +3467,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501239</v>
+        <v>131501242</v>
       </c>
       <c r="B29" t="n">
-        <v>80244</v>
+        <v>80239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>6441</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387579</v>
+        <v>387660</v>
       </c>
       <c r="R29" t="n">
-        <v>6618064</v>
+        <v>6617886</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3680,45 +3680,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501223</v>
+        <v>131501208</v>
       </c>
       <c r="B31" t="n">
-        <v>83231</v>
+        <v>57901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387587</v>
+        <v>387565</v>
       </c>
       <c r="R31" t="n">
-        <v>6617454</v>
+        <v>6617589</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3751,6 +3759,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3777,7 +3790,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501208</v>
+        <v>131501204</v>
       </c>
       <c r="B32" t="n">
         <v>57901</v>
@@ -3820,10 +3833,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387565</v>
+        <v>387618</v>
       </c>
       <c r="R32" t="n">
-        <v>6617589</v>
+        <v>6618118</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3887,7 +3900,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501204</v>
+        <v>131501211</v>
       </c>
       <c r="B33" t="n">
         <v>57901</v>
@@ -3920,7 +3933,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3930,10 +3943,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387618</v>
+        <v>387554</v>
       </c>
       <c r="R33" t="n">
-        <v>6618118</v>
+        <v>6617473</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3966,11 +3979,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3997,53 +4005,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501211</v>
+        <v>131501223</v>
       </c>
       <c r="B34" t="n">
-        <v>57901</v>
+        <v>83231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387554</v>
+        <v>387587</v>
       </c>
       <c r="R34" t="n">
-        <v>6617473</v>
+        <v>6617454</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4887,53 +4887,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501209</v>
+        <v>131501240</v>
       </c>
       <c r="B43" t="n">
-        <v>57901</v>
+        <v>80244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387543</v>
+        <v>387597</v>
       </c>
       <c r="R43" t="n">
-        <v>6617571</v>
+        <v>6618067</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4968,17 +4960,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4997,10 +4985,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501240</v>
+        <v>131501220</v>
       </c>
       <c r="B44" t="n">
-        <v>80244</v>
+        <v>92298</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5008,21 +4996,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5032,10 +5020,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387597</v>
+        <v>387620</v>
       </c>
       <c r="R44" t="n">
-        <v>6618067</v>
+        <v>6618075</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5076,7 +5064,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5095,32 +5082,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501220</v>
+        <v>131501196</v>
       </c>
       <c r="B45" t="n">
-        <v>92298</v>
+        <v>91801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5130,10 +5117,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387620</v>
+        <v>387554</v>
       </c>
       <c r="R45" t="n">
-        <v>6618075</v>
+        <v>6617465</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5192,45 +5179,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501196</v>
+        <v>131501209</v>
       </c>
       <c r="B46" t="n">
-        <v>91801</v>
+        <v>57901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387554</v>
+        <v>387543</v>
       </c>
       <c r="R46" t="n">
-        <v>6617465</v>
+        <v>6617571</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5263,6 +5258,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5881,32 +5881,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501263</v>
+        <v>131501236</v>
       </c>
       <c r="B53" t="n">
-        <v>80244</v>
+        <v>79266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387610</v>
+        <v>387557</v>
       </c>
       <c r="R53" t="n">
-        <v>6617561</v>
+        <v>6617549</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5960,7 +5960,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6089,32 +6088,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501218</v>
+        <v>131501263</v>
       </c>
       <c r="B55" t="n">
-        <v>80275</v>
+        <v>80244</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6124,10 +6123,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387575</v>
+        <v>387610</v>
       </c>
       <c r="R55" t="n">
-        <v>6617729</v>
+        <v>6617561</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6168,6 +6167,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6186,32 +6186,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501236</v>
+        <v>131501218</v>
       </c>
       <c r="B56" t="n">
-        <v>79266</v>
+        <v>80275</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6221,10 +6221,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387557</v>
+        <v>387575</v>
       </c>
       <c r="R56" t="n">
-        <v>6617549</v>
+        <v>6617729</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131819186</v>
+        <v>131821732</v>
       </c>
       <c r="B61" t="n">
-        <v>57092</v>
+        <v>80331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6747,53 +6747,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>387618</v>
+        <v>387538</v>
       </c>
       <c r="R61" t="n">
-        <v>6618030</v>
+        <v>6617660</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,7 +6806,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6835,12 +6816,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6867,10 +6843,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131821732</v>
+        <v>131819186</v>
       </c>
       <c r="B62" t="n">
-        <v>80331</v>
+        <v>57092</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,34 +6854,53 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387538</v>
+        <v>387618</v>
       </c>
       <c r="R62" t="n">
-        <v>6617660</v>
+        <v>6618030</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6937,7 +6932,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6947,7 +6942,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7444,48 +7444,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B67" t="n">
-        <v>92298</v>
+        <v>57095</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R67" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7514,7 +7523,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7524,7 +7533,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7539,69 +7553,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B68" t="n">
-        <v>57095</v>
+        <v>92298</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R68" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7630,7 +7635,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7640,12 +7645,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -2999,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501214</v>
+        <v>131501224</v>
       </c>
       <c r="B24" t="n">
-        <v>80275</v>
+        <v>80331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3010,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
         <v>387594</v>
       </c>
       <c r="R24" t="n">
-        <v>6618061</v>
+        <v>6617760</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501224</v>
+        <v>131501214</v>
       </c>
       <c r="B26" t="n">
-        <v>80331</v>
+        <v>80275</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
         <v>387594</v>
       </c>
       <c r="R26" t="n">
-        <v>6617760</v>
+        <v>6618061</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501239</v>
+        <v>131501259</v>
       </c>
       <c r="B27" t="n">
-        <v>80244</v>
+        <v>80406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387579</v>
+        <v>387611</v>
       </c>
       <c r="R27" t="n">
-        <v>6618064</v>
+        <v>6617519</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3369,7 +3369,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3388,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501259</v>
+        <v>131501242</v>
       </c>
       <c r="B28" t="n">
-        <v>80406</v>
+        <v>80239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3398,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6441</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387611</v>
+        <v>387660</v>
       </c>
       <c r="R28" t="n">
-        <v>6617519</v>
+        <v>6617886</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,6 +3466,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501242</v>
+        <v>131501239</v>
       </c>
       <c r="B29" t="n">
-        <v>80239</v>
+        <v>80244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6441</v>
+        <v>392</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387660</v>
+        <v>387579</v>
       </c>
       <c r="R29" t="n">
-        <v>6617886</v>
+        <v>6618064</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3680,53 +3680,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501208</v>
+        <v>131501223</v>
       </c>
       <c r="B31" t="n">
-        <v>57901</v>
+        <v>83231</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387565</v>
+        <v>387587</v>
       </c>
       <c r="R31" t="n">
-        <v>6617589</v>
+        <v>6617454</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3759,11 +3751,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3790,7 +3777,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501204</v>
+        <v>131501208</v>
       </c>
       <c r="B32" t="n">
         <v>57901</v>
@@ -3833,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387618</v>
+        <v>387565</v>
       </c>
       <c r="R32" t="n">
-        <v>6618118</v>
+        <v>6617589</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3900,7 +3887,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501211</v>
+        <v>131501204</v>
       </c>
       <c r="B33" t="n">
         <v>57901</v>
@@ -3933,7 +3920,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3943,10 +3930,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387554</v>
+        <v>387618</v>
       </c>
       <c r="R33" t="n">
-        <v>6617473</v>
+        <v>6618118</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3979,6 +3966,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4005,45 +3997,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501223</v>
+        <v>131501211</v>
       </c>
       <c r="B34" t="n">
-        <v>83231</v>
+        <v>57901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387587</v>
+        <v>387554</v>
       </c>
       <c r="R34" t="n">
-        <v>6617454</v>
+        <v>6617473</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -7444,57 +7444,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B67" t="n">
-        <v>57095</v>
+        <v>92298</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R67" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7523,7 +7514,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7533,12 +7524,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,60 +7539,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B68" t="n">
-        <v>92298</v>
+        <v>57095</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R68" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7635,7 +7630,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7645,7 +7640,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1817,45 +1817,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B12" t="n">
-        <v>80331</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R12" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1914,53 +1922,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B13" t="n">
-        <v>57901</v>
+        <v>80331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R13" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501259</v>
+        <v>131501239</v>
       </c>
       <c r="B27" t="n">
-        <v>80406</v>
+        <v>80244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387611</v>
+        <v>387579</v>
       </c>
       <c r="R27" t="n">
-        <v>6617519</v>
+        <v>6618064</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3369,6 +3369,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3387,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501242</v>
+        <v>131501259</v>
       </c>
       <c r="B28" t="n">
-        <v>80239</v>
+        <v>80406</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6441</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3422,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387660</v>
+        <v>387611</v>
       </c>
       <c r="R28" t="n">
-        <v>6617886</v>
+        <v>6617519</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3466,7 +3467,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501239</v>
+        <v>131501242</v>
       </c>
       <c r="B29" t="n">
-        <v>80244</v>
+        <v>80239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>6441</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387579</v>
+        <v>387660</v>
       </c>
       <c r="R29" t="n">
-        <v>6618064</v>
+        <v>6617886</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -4887,45 +4887,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501240</v>
+        <v>131501209</v>
       </c>
       <c r="B43" t="n">
-        <v>80244</v>
+        <v>57901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>392</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387597</v>
+        <v>387543</v>
       </c>
       <c r="R43" t="n">
-        <v>6618067</v>
+        <v>6617571</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4960,13 +4968,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4985,10 +4997,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501220</v>
+        <v>131501240</v>
       </c>
       <c r="B44" t="n">
-        <v>92298</v>
+        <v>80244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4996,21 +5008,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>392</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5020,10 +5032,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387620</v>
+        <v>387597</v>
       </c>
       <c r="R44" t="n">
-        <v>6618075</v>
+        <v>6618067</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5064,6 +5076,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5082,32 +5095,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501196</v>
+        <v>131501220</v>
       </c>
       <c r="B45" t="n">
-        <v>91801</v>
+        <v>92298</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5117,10 +5130,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387554</v>
+        <v>387620</v>
       </c>
       <c r="R45" t="n">
-        <v>6617465</v>
+        <v>6618075</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5179,53 +5192,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501209</v>
+        <v>131501196</v>
       </c>
       <c r="B46" t="n">
-        <v>57901</v>
+        <v>91801</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387543</v>
+        <v>387554</v>
       </c>
       <c r="R46" t="n">
-        <v>6617571</v>
+        <v>6617465</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5258,11 +5263,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5881,32 +5881,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501236</v>
+        <v>131501263</v>
       </c>
       <c r="B53" t="n">
-        <v>79266</v>
+        <v>80244</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387557</v>
+        <v>387610</v>
       </c>
       <c r="R53" t="n">
-        <v>6617549</v>
+        <v>6617561</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5960,6 +5960,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6088,32 +6089,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501263</v>
+        <v>131501218</v>
       </c>
       <c r="B55" t="n">
-        <v>80244</v>
+        <v>80275</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6123,10 +6124,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387610</v>
+        <v>387575</v>
       </c>
       <c r="R55" t="n">
-        <v>6617561</v>
+        <v>6617729</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6167,7 +6168,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6186,32 +6186,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501218</v>
+        <v>131501236</v>
       </c>
       <c r="B56" t="n">
-        <v>80275</v>
+        <v>79266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6221,10 +6221,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387575</v>
+        <v>387557</v>
       </c>
       <c r="R56" t="n">
-        <v>6617729</v>
+        <v>6617549</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -7444,48 +7444,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B67" t="n">
-        <v>92298</v>
+        <v>57095</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R67" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7514,7 +7523,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7524,7 +7533,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7539,69 +7553,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B68" t="n">
-        <v>57095</v>
+        <v>92298</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R68" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7630,7 +7635,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7640,12 +7645,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1817,53 +1817,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B12" t="n">
-        <v>57901</v>
+        <v>80331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R12" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1922,45 +1914,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B13" t="n">
-        <v>80331</v>
+        <v>57901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R13" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B16" t="n">
-        <v>57092</v>
+        <v>80406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,42 +2225,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R16" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2319,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B17" t="n">
-        <v>80406</v>
+        <v>57092</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2322,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R17" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -3680,45 +3680,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501223</v>
+        <v>131501208</v>
       </c>
       <c r="B31" t="n">
-        <v>83231</v>
+        <v>57901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387587</v>
+        <v>387565</v>
       </c>
       <c r="R31" t="n">
-        <v>6617454</v>
+        <v>6617589</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3751,6 +3759,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3777,7 +3790,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501208</v>
+        <v>131501204</v>
       </c>
       <c r="B32" t="n">
         <v>57901</v>
@@ -3820,10 +3833,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387565</v>
+        <v>387618</v>
       </c>
       <c r="R32" t="n">
-        <v>6617589</v>
+        <v>6618118</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3887,7 +3900,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501204</v>
+        <v>131501211</v>
       </c>
       <c r="B33" t="n">
         <v>57901</v>
@@ -3920,7 +3933,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3930,10 +3943,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387618</v>
+        <v>387554</v>
       </c>
       <c r="R33" t="n">
-        <v>6618118</v>
+        <v>6617473</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3966,11 +3979,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3997,53 +4005,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501211</v>
+        <v>131501223</v>
       </c>
       <c r="B34" t="n">
-        <v>57901</v>
+        <v>83231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387554</v>
+        <v>387587</v>
       </c>
       <c r="R34" t="n">
-        <v>6617473</v>
+        <v>6617454</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4887,53 +4887,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501209</v>
+        <v>131501240</v>
       </c>
       <c r="B43" t="n">
-        <v>57901</v>
+        <v>80244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387543</v>
+        <v>387597</v>
       </c>
       <c r="R43" t="n">
-        <v>6617571</v>
+        <v>6618067</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4968,17 +4960,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4997,10 +4985,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501240</v>
+        <v>131501220</v>
       </c>
       <c r="B44" t="n">
-        <v>80244</v>
+        <v>92298</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5008,21 +4996,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5032,10 +5020,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387597</v>
+        <v>387620</v>
       </c>
       <c r="R44" t="n">
-        <v>6618067</v>
+        <v>6618075</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5076,7 +5064,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5095,32 +5082,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501220</v>
+        <v>131501196</v>
       </c>
       <c r="B45" t="n">
-        <v>92298</v>
+        <v>91801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5130,10 +5117,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387620</v>
+        <v>387554</v>
       </c>
       <c r="R45" t="n">
-        <v>6618075</v>
+        <v>6617465</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5192,45 +5179,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501196</v>
+        <v>131501209</v>
       </c>
       <c r="B46" t="n">
-        <v>91801</v>
+        <v>57901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387554</v>
+        <v>387543</v>
       </c>
       <c r="R46" t="n">
-        <v>6617465</v>
+        <v>6617571</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5263,6 +5258,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1817,45 +1817,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B12" t="n">
-        <v>80331</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R12" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1914,53 +1922,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B13" t="n">
-        <v>57901</v>
+        <v>80331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R13" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501224</v>
+        <v>131501214</v>
       </c>
       <c r="B24" t="n">
-        <v>80331</v>
+        <v>80275</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3010,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
         <v>387594</v>
       </c>
       <c r="R24" t="n">
-        <v>6617760</v>
+        <v>6618061</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501214</v>
+        <v>131501224</v>
       </c>
       <c r="B26" t="n">
-        <v>80275</v>
+        <v>80331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
         <v>387594</v>
       </c>
       <c r="R26" t="n">
-        <v>6618061</v>
+        <v>6617760</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3680,53 +3680,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501208</v>
+        <v>131501223</v>
       </c>
       <c r="B31" t="n">
-        <v>57901</v>
+        <v>83231</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387565</v>
+        <v>387587</v>
       </c>
       <c r="R31" t="n">
-        <v>6617589</v>
+        <v>6617454</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3759,11 +3751,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3790,7 +3777,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501204</v>
+        <v>131501208</v>
       </c>
       <c r="B32" t="n">
         <v>57901</v>
@@ -3833,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387618</v>
+        <v>387565</v>
       </c>
       <c r="R32" t="n">
-        <v>6618118</v>
+        <v>6617589</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3900,7 +3887,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501211</v>
+        <v>131501204</v>
       </c>
       <c r="B33" t="n">
         <v>57901</v>
@@ -3933,7 +3920,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3943,10 +3930,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387554</v>
+        <v>387618</v>
       </c>
       <c r="R33" t="n">
-        <v>6617473</v>
+        <v>6618118</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3979,6 +3966,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4005,45 +3997,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501223</v>
+        <v>131501211</v>
       </c>
       <c r="B34" t="n">
-        <v>83231</v>
+        <v>57901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387587</v>
+        <v>387554</v>
       </c>
       <c r="R34" t="n">
-        <v>6617454</v>
+        <v>6617473</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501263</v>
+        <v>131501236</v>
       </c>
       <c r="B53" t="n">
-        <v>80244</v>
+        <v>79266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387610</v>
+        <v>387557</v>
       </c>
       <c r="R53" t="n">
-        <v>6617561</v>
+        <v>6617549</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5960,7 +5960,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6089,32 +6088,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501218</v>
+        <v>131501263</v>
       </c>
       <c r="B55" t="n">
-        <v>80275</v>
+        <v>80244</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6124,10 +6123,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387575</v>
+        <v>387610</v>
       </c>
       <c r="R55" t="n">
-        <v>6617729</v>
+        <v>6617561</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6168,6 +6167,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6186,32 +6186,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501236</v>
+        <v>131501218</v>
       </c>
       <c r="B56" t="n">
-        <v>79266</v>
+        <v>80275</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6221,10 +6221,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387557</v>
+        <v>387575</v>
       </c>
       <c r="R56" t="n">
-        <v>6617549</v>
+        <v>6617729</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131821732</v>
+        <v>131819186</v>
       </c>
       <c r="B61" t="n">
-        <v>80331</v>
+        <v>57092</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6747,34 +6747,53 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>387538</v>
+        <v>387618</v>
       </c>
       <c r="R61" t="n">
-        <v>6617660</v>
+        <v>6618030</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6806,7 +6825,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6816,7 +6835,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6843,10 +6867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131819186</v>
+        <v>131821732</v>
       </c>
       <c r="B62" t="n">
-        <v>57092</v>
+        <v>80331</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6854,53 +6878,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387618</v>
+        <v>387538</v>
       </c>
       <c r="R62" t="n">
-        <v>6618030</v>
+        <v>6617660</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6937,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6942,12 +6947,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7444,57 +7444,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B67" t="n">
-        <v>57095</v>
+        <v>92298</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R67" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7523,7 +7514,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7533,12 +7524,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,60 +7539,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B68" t="n">
-        <v>92298</v>
+        <v>57095</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R68" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7635,7 +7630,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7645,7 +7640,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>131501250</v>
       </c>
       <c r="B8" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131501249</v>
       </c>
       <c r="B9" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131501213</v>
       </c>
       <c r="B10" t="n">
-        <v>80275</v>
+        <v>80278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>131501235</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,53 +1817,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B12" t="n">
-        <v>57901</v>
+        <v>80334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R12" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1922,45 +1914,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B13" t="n">
-        <v>80331</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R13" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131501247</v>
+        <v>131501195</v>
       </c>
       <c r="B14" t="n">
-        <v>80244</v>
+        <v>91804</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387568</v>
+        <v>387619</v>
       </c>
       <c r="R14" t="n">
-        <v>6618040</v>
+        <v>6618073</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2098,7 +2098,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2117,32 +2116,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131501195</v>
+        <v>131501247</v>
       </c>
       <c r="B15" t="n">
-        <v>91801</v>
+        <v>80247</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2152,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387619</v>
+        <v>387568</v>
       </c>
       <c r="R15" t="n">
-        <v>6618073</v>
+        <v>6618040</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2196,6 +2195,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B16" t="n">
-        <v>80406</v>
+        <v>57095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,34 +2225,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R16" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2311,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B17" t="n">
-        <v>57092</v>
+        <v>80409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,42 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R17" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2419,7 +2419,7 @@
         <v>131501227</v>
       </c>
       <c r="B18" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131501229</v>
       </c>
       <c r="B19" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131501228</v>
       </c>
       <c r="B20" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>131501216</v>
       </c>
       <c r="B21" t="n">
-        <v>80275</v>
+        <v>80278</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>131501194</v>
       </c>
       <c r="B22" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>131501201</v>
       </c>
       <c r="B23" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501214</v>
+        <v>131501233</v>
       </c>
       <c r="B24" t="n">
-        <v>80275</v>
+        <v>79269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387594</v>
+        <v>387666</v>
       </c>
       <c r="R24" t="n">
-        <v>6618061</v>
+        <v>6618011</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3096,32 +3096,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131501233</v>
+        <v>131501214</v>
       </c>
       <c r="B25" t="n">
-        <v>79266</v>
+        <v>80278</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387666</v>
+        <v>387594</v>
       </c>
       <c r="R25" t="n">
-        <v>6618011</v>
+        <v>6618061</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3196,7 +3196,7 @@
         <v>131501224</v>
       </c>
       <c r="B26" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>131501239</v>
       </c>
       <c r="B27" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501259</v>
+        <v>131501242</v>
       </c>
       <c r="B28" t="n">
-        <v>80406</v>
+        <v>80242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6441</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387611</v>
+        <v>387660</v>
       </c>
       <c r="R28" t="n">
-        <v>6617519</v>
+        <v>6617886</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,6 +3467,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,10 +3486,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501242</v>
+        <v>131501259</v>
       </c>
       <c r="B29" t="n">
-        <v>80239</v>
+        <v>80409</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3496,16 +3497,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6441</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3520,10 +3521,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387660</v>
+        <v>387611</v>
       </c>
       <c r="R29" t="n">
-        <v>6617886</v>
+        <v>6617519</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3564,7 +3565,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>131501253</v>
       </c>
       <c r="B30" t="n">
-        <v>80406</v>
+        <v>80409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>131501223</v>
       </c>
       <c r="B31" t="n">
-        <v>83231</v>
+        <v>83234</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501208</v>
+        <v>131501211</v>
       </c>
       <c r="B32" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387565</v>
+        <v>387554</v>
       </c>
       <c r="R32" t="n">
-        <v>6617589</v>
+        <v>6617473</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3856,11 +3856,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3890,7 +3885,7 @@
         <v>131501204</v>
       </c>
       <c r="B33" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3997,10 +3992,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501211</v>
+        <v>131501208</v>
       </c>
       <c r="B34" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4030,7 +4025,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4040,10 +4035,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387554</v>
+        <v>387565</v>
       </c>
       <c r="R34" t="n">
-        <v>6617473</v>
+        <v>6617589</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4076,6 +4071,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4105,7 +4105,7 @@
         <v>131501244</v>
       </c>
       <c r="B35" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>131501246</v>
       </c>
       <c r="B36" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>131501255</v>
       </c>
       <c r="B37" t="n">
-        <v>80406</v>
+        <v>80409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>131501222</v>
       </c>
       <c r="B38" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>131501248</v>
       </c>
       <c r="B39" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>131501238</v>
       </c>
       <c r="B40" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>131501245</v>
       </c>
       <c r="B41" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>131501234</v>
       </c>
       <c r="B42" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501240</v>
+        <v>131501220</v>
       </c>
       <c r="B43" t="n">
-        <v>80244</v>
+        <v>92301</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,21 +4898,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>392</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387597</v>
+        <v>387620</v>
       </c>
       <c r="R43" t="n">
-        <v>6618067</v>
+        <v>6618075</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4966,7 +4966,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4985,32 +4984,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501220</v>
+        <v>131501196</v>
       </c>
       <c r="B44" t="n">
-        <v>92298</v>
+        <v>91804</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5020,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387620</v>
+        <v>387554</v>
       </c>
       <c r="R44" t="n">
-        <v>6618075</v>
+        <v>6617465</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5082,45 +5081,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501196</v>
+        <v>131501209</v>
       </c>
       <c r="B45" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387554</v>
+        <v>387543</v>
       </c>
       <c r="R45" t="n">
-        <v>6617465</v>
+        <v>6617571</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5153,6 +5160,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5179,53 +5191,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501209</v>
+        <v>131501240</v>
       </c>
       <c r="B46" t="n">
-        <v>57901</v>
+        <v>80247</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>392</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387543</v>
+        <v>387597</v>
       </c>
       <c r="R46" t="n">
-        <v>6617571</v>
+        <v>6618067</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5260,17 +5264,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131501212</v>
+        <v>131501261</v>
       </c>
       <c r="B47" t="n">
-        <v>80275</v>
+        <v>5179</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,34 +5300,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R47" t="n">
-        <v>6618057</v>
+        <v>6617556</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5368,6 +5377,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5386,10 +5396,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131501252</v>
+        <v>131501212</v>
       </c>
       <c r="B48" t="n">
-        <v>80406</v>
+        <v>80278</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5397,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5421,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387602</v>
+        <v>387577</v>
       </c>
       <c r="R48" t="n">
-        <v>6618110</v>
+        <v>6618057</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5483,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131501261</v>
+        <v>131501252</v>
       </c>
       <c r="B49" t="n">
-        <v>5178</v>
+        <v>80409</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5494,43 +5504,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387569</v>
+        <v>387602</v>
       </c>
       <c r="R49" t="n">
-        <v>6617556</v>
+        <v>6618110</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5571,7 +5572,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>131501215</v>
       </c>
       <c r="B50" t="n">
-        <v>80275</v>
+        <v>80278</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>131501226</v>
       </c>
       <c r="B51" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131501225</v>
       </c>
       <c r="B52" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501236</v>
+        <v>131501263</v>
       </c>
       <c r="B53" t="n">
-        <v>79266</v>
+        <v>80247</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387557</v>
+        <v>387610</v>
       </c>
       <c r="R53" t="n">
-        <v>6617549</v>
+        <v>6617561</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5960,6 +5960,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5978,53 +5979,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501210</v>
+        <v>131501218</v>
       </c>
       <c r="B54" t="n">
-        <v>57901</v>
+        <v>80278</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387596</v>
+        <v>387575</v>
       </c>
       <c r="R54" t="n">
-        <v>6617548</v>
+        <v>6617729</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6057,11 +6050,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6088,32 +6076,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501263</v>
+        <v>131501236</v>
       </c>
       <c r="B55" t="n">
-        <v>80244</v>
+        <v>79269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6123,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387610</v>
+        <v>387557</v>
       </c>
       <c r="R55" t="n">
-        <v>6617561</v>
+        <v>6617549</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6167,7 +6155,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6186,45 +6173,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501218</v>
+        <v>131501210</v>
       </c>
       <c r="B56" t="n">
-        <v>80275</v>
+        <v>57904</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387575</v>
+        <v>387596</v>
       </c>
       <c r="R56" t="n">
-        <v>6617729</v>
+        <v>6617548</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6257,6 +6252,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6286,7 +6286,7 @@
         <v>131501193</v>
       </c>
       <c r="B57" t="n">
-        <v>80244</v>
+        <v>80247</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131822720</v>
+        <v>131819716</v>
       </c>
       <c r="B58" t="n">
-        <v>57901</v>
+        <v>91862</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6416,12 +6416,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6430,10 +6425,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>387686</v>
+        <v>387662</v>
       </c>
       <c r="R58" t="n">
-        <v>6617861</v>
+        <v>6617924</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6465,7 +6460,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6475,7 +6470,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6502,10 +6497,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131819716</v>
+        <v>131822720</v>
       </c>
       <c r="B59" t="n">
-        <v>91859</v>
+        <v>57904</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,21 +6508,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6537,7 +6532,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387662</v>
+        <v>387686</v>
       </c>
       <c r="R59" t="n">
-        <v>6617924</v>
+        <v>6617861</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6621,7 +6621,7 @@
         <v>131816381</v>
       </c>
       <c r="B60" t="n">
-        <v>91859</v>
+        <v>91862</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>131819186</v>
       </c>
       <c r="B61" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>131821732</v>
       </c>
       <c r="B62" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>131815937</v>
       </c>
       <c r="B63" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>131822763</v>
       </c>
       <c r="B64" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>131819629</v>
       </c>
       <c r="B65" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>131820869</v>
       </c>
       <c r="B66" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7444,48 +7444,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B67" t="n">
-        <v>92298</v>
+        <v>57098</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R67" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7514,7 +7523,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7524,7 +7533,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7539,69 +7553,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B68" t="n">
-        <v>57095</v>
+        <v>92301</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R68" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7630,7 +7635,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7640,12 +7645,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7675,7 +7675,7 @@
         <v>131820835</v>
       </c>
       <c r="B69" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>131820604</v>
       </c>
       <c r="B70" t="n">
-        <v>80406</v>
+        <v>80409</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7885,10 +7885,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131815985</v>
+        <v>131821338</v>
       </c>
       <c r="B71" t="n">
-        <v>80400</v>
+        <v>75375</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7896,37 +7896,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387618</v>
+        <v>387631</v>
       </c>
       <c r="R71" t="n">
-        <v>6618030</v>
+        <v>6618098</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7980,22 +7980,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131821338</v>
+        <v>131815985</v>
       </c>
       <c r="B72" t="n">
-        <v>75372</v>
+        <v>80403</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8003,37 +8003,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387631</v>
+        <v>387618</v>
       </c>
       <c r="R72" t="n">
-        <v>6618098</v>
+        <v>6618030</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8087,12 +8087,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
         <v>131820383</v>
       </c>
       <c r="B73" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>131821100</v>
       </c>
       <c r="B74" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>131817086</v>
       </c>
       <c r="B75" t="n">
-        <v>90875</v>
+        <v>90878</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>131820504</v>
       </c>
       <c r="B76" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>131816272</v>
       </c>
       <c r="B77" t="n">
-        <v>8443</v>
+        <v>8444</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>131816249</v>
       </c>
       <c r="B78" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>131823453</v>
       </c>
       <c r="B79" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>131821057</v>
       </c>
       <c r="B80" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>131820532</v>
       </c>
       <c r="B81" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>131821233</v>
       </c>
       <c r="B82" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>131820813</v>
       </c>
       <c r="B83" t="n">
-        <v>80406</v>
+        <v>80409</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>131501250</v>
       </c>
       <c r="B8" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131501249</v>
       </c>
       <c r="B9" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131501213</v>
       </c>
       <c r="B10" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>131501235</v>
       </c>
       <c r="B11" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,45 +1817,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B12" t="n">
-        <v>80334</v>
+        <v>57909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R12" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1914,53 +1922,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>80339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R13" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2022,7 +2022,7 @@
         <v>131501195</v>
       </c>
       <c r="B14" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>131501247</v>
       </c>
       <c r="B15" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B16" t="n">
-        <v>57095</v>
+        <v>80414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,42 +2225,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R16" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2319,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B17" t="n">
-        <v>80409</v>
+        <v>57100</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2322,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R17" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2419,7 +2419,7 @@
         <v>131501227</v>
       </c>
       <c r="B18" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131501229</v>
       </c>
       <c r="B19" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131501228</v>
       </c>
       <c r="B20" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>131501216</v>
       </c>
       <c r="B21" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>131501194</v>
       </c>
       <c r="B22" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>131501201</v>
       </c>
       <c r="B23" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>131501233</v>
       </c>
       <c r="B24" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>131501214</v>
       </c>
       <c r="B25" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>131501224</v>
       </c>
       <c r="B26" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501239</v>
+        <v>131501242</v>
       </c>
       <c r="B27" t="n">
         <v>80247</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>392</v>
+        <v>6441</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387579</v>
+        <v>387660</v>
       </c>
       <c r="R27" t="n">
-        <v>6618064</v>
+        <v>6617886</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501242</v>
+        <v>131501259</v>
       </c>
       <c r="B28" t="n">
-        <v>80242</v>
+        <v>80414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6441</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387660</v>
+        <v>387611</v>
       </c>
       <c r="R28" t="n">
-        <v>6617886</v>
+        <v>6617519</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,7 +3467,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3486,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501259</v>
+        <v>131501239</v>
       </c>
       <c r="B29" t="n">
-        <v>80409</v>
+        <v>80252</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3521,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387611</v>
+        <v>387579</v>
       </c>
       <c r="R29" t="n">
-        <v>6617519</v>
+        <v>6618064</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3565,6 +3564,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>131501253</v>
       </c>
       <c r="B30" t="n">
-        <v>80409</v>
+        <v>80414</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>131501223</v>
       </c>
       <c r="B31" t="n">
-        <v>83234</v>
+        <v>83239</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3777,10 +3777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501211</v>
+        <v>131501208</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387554</v>
+        <v>387565</v>
       </c>
       <c r="R32" t="n">
-        <v>6617473</v>
+        <v>6617589</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3856,6 +3856,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3885,7 +3890,7 @@
         <v>131501204</v>
       </c>
       <c r="B33" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3992,10 +3997,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501208</v>
+        <v>131501211</v>
       </c>
       <c r="B34" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4025,7 +4030,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4035,10 +4040,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387565</v>
+        <v>387554</v>
       </c>
       <c r="R34" t="n">
-        <v>6617589</v>
+        <v>6617473</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4071,11 +4076,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4105,7 +4105,7 @@
         <v>131501244</v>
       </c>
       <c r="B35" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>131501246</v>
       </c>
       <c r="B36" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4298,45 +4298,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131501255</v>
+        <v>131501222</v>
       </c>
       <c r="B37" t="n">
-        <v>80409</v>
+        <v>92266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387660</v>
+        <v>387619</v>
       </c>
       <c r="R37" t="n">
-        <v>6617892</v>
+        <v>6618071</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4377,6 +4380,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4395,48 +4399,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131501222</v>
+        <v>131501255</v>
       </c>
       <c r="B38" t="n">
-        <v>92261</v>
+        <v>80414</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387619</v>
+        <v>387660</v>
       </c>
       <c r="R38" t="n">
-        <v>6618071</v>
+        <v>6617892</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4477,7 +4478,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>131501248</v>
       </c>
       <c r="B39" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>131501238</v>
       </c>
       <c r="B40" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>131501245</v>
       </c>
       <c r="B41" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>131501234</v>
       </c>
       <c r="B42" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4887,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501220</v>
+        <v>131501240</v>
       </c>
       <c r="B43" t="n">
-        <v>92301</v>
+        <v>80252</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4898,21 +4898,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>392</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387620</v>
+        <v>387597</v>
       </c>
       <c r="R43" t="n">
-        <v>6618075</v>
+        <v>6618067</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4966,6 +4966,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4984,32 +4985,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501196</v>
+        <v>131501220</v>
       </c>
       <c r="B44" t="n">
-        <v>91804</v>
+        <v>92306</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,10 +5020,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387554</v>
+        <v>387620</v>
       </c>
       <c r="R44" t="n">
-        <v>6617465</v>
+        <v>6618075</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5084,7 +5085,7 @@
         <v>131501209</v>
       </c>
       <c r="B45" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5191,32 +5192,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501240</v>
+        <v>131501196</v>
       </c>
       <c r="B46" t="n">
-        <v>80247</v>
+        <v>91809</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5226,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387597</v>
+        <v>387554</v>
       </c>
       <c r="R46" t="n">
-        <v>6618067</v>
+        <v>6617465</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5270,7 +5271,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131501261</v>
+        <v>131501212</v>
       </c>
       <c r="B47" t="n">
-        <v>5179</v>
+        <v>80283</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5300,43 +5300,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387569</v>
+        <v>387577</v>
       </c>
       <c r="R47" t="n">
-        <v>6617556</v>
+        <v>6618057</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5377,7 +5368,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5396,10 +5386,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131501212</v>
+        <v>131501252</v>
       </c>
       <c r="B48" t="n">
-        <v>80278</v>
+        <v>80414</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,21 +5397,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5421,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387577</v>
+        <v>387602</v>
       </c>
       <c r="R48" t="n">
-        <v>6618057</v>
+        <v>6618110</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5493,10 +5483,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131501252</v>
+        <v>131501261</v>
       </c>
       <c r="B49" t="n">
-        <v>80409</v>
+        <v>5179</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5504,34 +5494,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387602</v>
+        <v>387569</v>
       </c>
       <c r="R49" t="n">
-        <v>6618110</v>
+        <v>6617556</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5572,6 +5571,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>131501215</v>
       </c>
       <c r="B50" t="n">
-        <v>80278</v>
+        <v>80283</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>131501226</v>
       </c>
       <c r="B51" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131501225</v>
       </c>
       <c r="B52" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>131501263</v>
       </c>
       <c r="B53" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5979,45 +5979,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501218</v>
+        <v>131501210</v>
       </c>
       <c r="B54" t="n">
-        <v>80278</v>
+        <v>57909</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387575</v>
+        <v>387596</v>
       </c>
       <c r="R54" t="n">
-        <v>6617729</v>
+        <v>6617548</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6050,6 +6058,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6076,32 +6089,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501236</v>
+        <v>131501218</v>
       </c>
       <c r="B55" t="n">
-        <v>79269</v>
+        <v>80283</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6111,10 +6124,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387557</v>
+        <v>387575</v>
       </c>
       <c r="R55" t="n">
-        <v>6617549</v>
+        <v>6617729</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6173,10 +6186,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501210</v>
+        <v>131501236</v>
       </c>
       <c r="B56" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6184,42 +6197,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387596</v>
+        <v>387557</v>
       </c>
       <c r="R56" t="n">
-        <v>6617548</v>
+        <v>6617549</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6252,11 +6257,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6286,7 +6286,7 @@
         <v>131501193</v>
       </c>
       <c r="B57" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>131819716</v>
       </c>
       <c r="B58" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>131822720</v>
       </c>
       <c r="B59" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>131816381</v>
       </c>
       <c r="B60" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>131819186</v>
       </c>
       <c r="B61" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>131821732</v>
       </c>
       <c r="B62" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>131815937</v>
       </c>
       <c r="B63" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>131822763</v>
       </c>
       <c r="B64" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>131819629</v>
       </c>
       <c r="B65" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>131820869</v>
       </c>
       <c r="B66" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7444,57 +7444,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B67" t="n">
-        <v>57098</v>
+        <v>92306</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R67" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7523,7 +7514,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7533,12 +7524,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,60 +7539,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B68" t="n">
-        <v>92301</v>
+        <v>57103</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R68" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7635,7 +7630,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7645,7 +7640,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7675,7 +7675,7 @@
         <v>131820835</v>
       </c>
       <c r="B69" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>131820604</v>
       </c>
       <c r="B70" t="n">
-        <v>80409</v>
+        <v>80414</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>131821338</v>
       </c>
       <c r="B71" t="n">
-        <v>75375</v>
+        <v>75380</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>131815985</v>
       </c>
       <c r="B72" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>131820383</v>
       </c>
       <c r="B73" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8206,62 +8206,59 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131821100</v>
+        <v>131817086</v>
       </c>
       <c r="B74" t="n">
-        <v>99047</v>
+        <v>90883</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>889</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387541</v>
+        <v>387612</v>
       </c>
       <c r="R74" t="n">
-        <v>6617620</v>
+        <v>6618032</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8290,7 +8287,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8300,7 +8297,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8315,71 +8312,74 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131817086</v>
+        <v>131821100</v>
       </c>
       <c r="B75" t="n">
-        <v>90878</v>
+        <v>99052</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>889</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387612</v>
+        <v>387541</v>
       </c>
       <c r="R75" t="n">
-        <v>6618032</v>
+        <v>6617620</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8433,22 +8433,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131820504</v>
+        <v>131816272</v>
       </c>
       <c r="B76" t="n">
-        <v>91804</v>
+        <v>8444</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8456,34 +8456,48 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387672</v>
+        <v>387612</v>
       </c>
       <c r="R76" t="n">
-        <v>6617684</v>
+        <v>6618060</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8515,7 +8529,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8525,7 +8539,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8552,10 +8566,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131816272</v>
+        <v>131820504</v>
       </c>
       <c r="B77" t="n">
-        <v>8444</v>
+        <v>91809</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8563,48 +8577,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387612</v>
+        <v>387672</v>
       </c>
       <c r="R77" t="n">
-        <v>6618060</v>
+        <v>6617684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8676,7 +8676,7 @@
         <v>131816249</v>
       </c>
       <c r="B78" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>131823453</v>
       </c>
       <c r="B79" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>131820532</v>
       </c>
       <c r="B81" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>131820813</v>
       </c>
       <c r="B83" t="n">
-        <v>80409</v>
+        <v>80414</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1817,53 +1817,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B12" t="n">
-        <v>57909</v>
+        <v>80339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R12" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1922,45 +1914,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B13" t="n">
-        <v>80339</v>
+        <v>57909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R13" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131501195</v>
+        <v>131501247</v>
       </c>
       <c r="B14" t="n">
-        <v>91809</v>
+        <v>80252</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387619</v>
+        <v>387568</v>
       </c>
       <c r="R14" t="n">
-        <v>6618073</v>
+        <v>6618040</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2098,6 +2098,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2116,32 +2117,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131501247</v>
+        <v>131501195</v>
       </c>
       <c r="B15" t="n">
-        <v>80252</v>
+        <v>91809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387568</v>
+        <v>387619</v>
       </c>
       <c r="R15" t="n">
-        <v>6618040</v>
+        <v>6618073</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2195,7 +2196,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B16" t="n">
-        <v>80414</v>
+        <v>57100</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,34 +2225,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R16" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2311,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B17" t="n">
-        <v>57100</v>
+        <v>80414</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,42 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R17" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501242</v>
+        <v>131501239</v>
       </c>
       <c r="B27" t="n">
-        <v>80247</v>
+        <v>80252</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6441</v>
+        <v>392</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387660</v>
+        <v>387579</v>
       </c>
       <c r="R27" t="n">
-        <v>6617886</v>
+        <v>6618064</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501259</v>
+        <v>131501242</v>
       </c>
       <c r="B28" t="n">
-        <v>80414</v>
+        <v>80247</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6441</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387611</v>
+        <v>387660</v>
       </c>
       <c r="R28" t="n">
-        <v>6617519</v>
+        <v>6617886</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,6 +3467,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,32 +3486,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501239</v>
+        <v>131501259</v>
       </c>
       <c r="B29" t="n">
-        <v>80252</v>
+        <v>80414</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3521,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387579</v>
+        <v>387611</v>
       </c>
       <c r="R29" t="n">
-        <v>6618064</v>
+        <v>6617519</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3564,7 +3565,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501253</v>
+        <v>131501223</v>
       </c>
       <c r="B30" t="n">
-        <v>80414</v>
+        <v>83239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387583</v>
+        <v>387587</v>
       </c>
       <c r="R30" t="n">
-        <v>6618100</v>
+        <v>6617454</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501223</v>
+        <v>131501253</v>
       </c>
       <c r="B31" t="n">
-        <v>83239</v>
+        <v>80414</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>306</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387587</v>
+        <v>387583</v>
       </c>
       <c r="R31" t="n">
-        <v>6617454</v>
+        <v>6618100</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -5082,53 +5082,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501209</v>
+        <v>131501196</v>
       </c>
       <c r="B45" t="n">
-        <v>57909</v>
+        <v>91809</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387543</v>
+        <v>387554</v>
       </c>
       <c r="R45" t="n">
-        <v>6617571</v>
+        <v>6617465</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5161,11 +5153,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5192,45 +5179,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501196</v>
+        <v>131501209</v>
       </c>
       <c r="B46" t="n">
-        <v>91809</v>
+        <v>57909</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387554</v>
+        <v>387543</v>
       </c>
       <c r="R46" t="n">
-        <v>6617465</v>
+        <v>6617571</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5263,6 +5258,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5979,53 +5979,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501210</v>
+        <v>131501218</v>
       </c>
       <c r="B54" t="n">
-        <v>57909</v>
+        <v>80283</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387596</v>
+        <v>387575</v>
       </c>
       <c r="R54" t="n">
-        <v>6617548</v>
+        <v>6617729</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6058,11 +6050,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6089,32 +6076,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501218</v>
+        <v>131501236</v>
       </c>
       <c r="B55" t="n">
-        <v>80283</v>
+        <v>79274</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6124,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387575</v>
+        <v>387557</v>
       </c>
       <c r="R55" t="n">
-        <v>6617729</v>
+        <v>6617549</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6186,10 +6173,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131501236</v>
+        <v>131501210</v>
       </c>
       <c r="B56" t="n">
-        <v>79274</v>
+        <v>57909</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6197,34 +6184,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387557</v>
+        <v>387596</v>
       </c>
       <c r="R56" t="n">
-        <v>6617549</v>
+        <v>6617548</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6257,6 +6252,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>131501250</v>
       </c>
       <c r="B8" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131501249</v>
       </c>
       <c r="B9" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131501213</v>
       </c>
       <c r="B10" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>131501235</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,45 +1817,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B12" t="n">
-        <v>80339</v>
+        <v>57911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R12" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1914,53 +1922,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B13" t="n">
-        <v>57909</v>
+        <v>80341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R13" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2022,7 +2022,7 @@
         <v>131501247</v>
       </c>
       <c r="B14" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>131501195</v>
       </c>
       <c r="B15" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131501198</v>
+        <v>131501257</v>
       </c>
       <c r="B16" t="n">
-        <v>57100</v>
+        <v>80416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,42 +2225,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387679</v>
+        <v>387551</v>
       </c>
       <c r="R16" t="n">
-        <v>6617717</v>
+        <v>6617617</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2319,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131501257</v>
+        <v>131501198</v>
       </c>
       <c r="B17" t="n">
-        <v>80414</v>
+        <v>57102</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2322,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387551</v>
+        <v>387679</v>
       </c>
       <c r="R17" t="n">
-        <v>6617617</v>
+        <v>6617717</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2419,7 +2419,7 @@
         <v>131501227</v>
       </c>
       <c r="B18" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131501229</v>
       </c>
       <c r="B19" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131501228</v>
       </c>
       <c r="B20" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>131501216</v>
       </c>
       <c r="B21" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>131501194</v>
       </c>
       <c r="B22" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>131501201</v>
       </c>
       <c r="B23" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2999,32 +2999,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131501233</v>
+        <v>131501224</v>
       </c>
       <c r="B24" t="n">
-        <v>79274</v>
+        <v>80341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387666</v>
+        <v>387594</v>
       </c>
       <c r="R24" t="n">
-        <v>6618011</v>
+        <v>6617760</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3096,32 +3096,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131501214</v>
+        <v>131501233</v>
       </c>
       <c r="B25" t="n">
-        <v>80283</v>
+        <v>79276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387594</v>
+        <v>387666</v>
       </c>
       <c r="R25" t="n">
-        <v>6618061</v>
+        <v>6618011</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131501224</v>
+        <v>131501214</v>
       </c>
       <c r="B26" t="n">
-        <v>80339</v>
+        <v>80285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
         <v>387594</v>
       </c>
       <c r="R26" t="n">
-        <v>6617760</v>
+        <v>6618061</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501239</v>
+        <v>131501242</v>
       </c>
       <c r="B27" t="n">
-        <v>80252</v>
+        <v>80249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>392</v>
+        <v>6441</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387579</v>
+        <v>387660</v>
       </c>
       <c r="R27" t="n">
-        <v>6618064</v>
+        <v>6617886</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501242</v>
+        <v>131501259</v>
       </c>
       <c r="B28" t="n">
-        <v>80247</v>
+        <v>80416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6441</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387660</v>
+        <v>387611</v>
       </c>
       <c r="R28" t="n">
-        <v>6617886</v>
+        <v>6617519</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,7 +3467,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3486,32 +3485,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501259</v>
+        <v>131501239</v>
       </c>
       <c r="B29" t="n">
-        <v>80414</v>
+        <v>80254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3521,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387611</v>
+        <v>387579</v>
       </c>
       <c r="R29" t="n">
-        <v>6617519</v>
+        <v>6618064</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3565,6 +3564,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501223</v>
+        <v>131501253</v>
       </c>
       <c r="B30" t="n">
-        <v>83239</v>
+        <v>80416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>306</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387587</v>
+        <v>387583</v>
       </c>
       <c r="R30" t="n">
-        <v>6617454</v>
+        <v>6618100</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501253</v>
+        <v>131501223</v>
       </c>
       <c r="B31" t="n">
-        <v>80414</v>
+        <v>83241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387583</v>
+        <v>387587</v>
       </c>
       <c r="R31" t="n">
-        <v>6618100</v>
+        <v>6617454</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3780,7 +3780,7 @@
         <v>131501208</v>
       </c>
       <c r="B32" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>131501204</v>
       </c>
       <c r="B33" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>131501211</v>
       </c>
       <c r="B34" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>131501244</v>
       </c>
       <c r="B35" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>131501246</v>
       </c>
       <c r="B36" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4298,48 +4298,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131501222</v>
+        <v>131501255</v>
       </c>
       <c r="B37" t="n">
-        <v>92266</v>
+        <v>80416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387619</v>
+        <v>387660</v>
       </c>
       <c r="R37" t="n">
-        <v>6618071</v>
+        <v>6617892</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4380,7 +4377,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4399,45 +4395,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131501255</v>
+        <v>131501222</v>
       </c>
       <c r="B38" t="n">
-        <v>80414</v>
+        <v>92268</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6040186</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387660</v>
+        <v>387619</v>
       </c>
       <c r="R38" t="n">
-        <v>6617892</v>
+        <v>6618071</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4478,6 +4477,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131501248</v>
+        <v>131501234</v>
       </c>
       <c r="B39" t="n">
-        <v>80252</v>
+        <v>79276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387575</v>
+        <v>387610</v>
       </c>
       <c r="R39" t="n">
-        <v>6618043</v>
+        <v>6617762</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4575,7 +4575,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4594,10 +4593,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131501238</v>
+        <v>131501248</v>
       </c>
       <c r="B40" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4629,10 +4628,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387572</v>
+        <v>387575</v>
       </c>
       <c r="R40" t="n">
-        <v>6618061</v>
+        <v>6618043</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4692,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131501245</v>
+        <v>131501238</v>
       </c>
       <c r="B41" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4727,10 +4726,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387569</v>
+        <v>387572</v>
       </c>
       <c r="R41" t="n">
-        <v>6617723</v>
+        <v>6618061</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4790,32 +4789,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131501234</v>
+        <v>131501245</v>
       </c>
       <c r="B42" t="n">
-        <v>79274</v>
+        <v>80254</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387610</v>
+        <v>387569</v>
       </c>
       <c r="R42" t="n">
-        <v>6617762</v>
+        <v>6617723</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4869,6 +4868,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4887,32 +4887,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501240</v>
+        <v>131501196</v>
       </c>
       <c r="B43" t="n">
-        <v>80252</v>
+        <v>91811</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387597</v>
+        <v>387554</v>
       </c>
       <c r="R43" t="n">
-        <v>6618067</v>
+        <v>6617465</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4966,7 +4966,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4985,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501220</v>
+        <v>131501240</v>
       </c>
       <c r="B44" t="n">
-        <v>92306</v>
+        <v>80254</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4996,21 +4995,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>392</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5020,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387620</v>
+        <v>387597</v>
       </c>
       <c r="R44" t="n">
-        <v>6618075</v>
+        <v>6618067</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5064,6 +5063,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5082,32 +5082,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501196</v>
+        <v>131501220</v>
       </c>
       <c r="B45" t="n">
-        <v>91809</v>
+        <v>92308</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387554</v>
+        <v>387620</v>
       </c>
       <c r="R45" t="n">
-        <v>6617465</v>
+        <v>6618075</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5182,7 +5182,7 @@
         <v>131501209</v>
       </c>
       <c r="B46" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>131501212</v>
       </c>
       <c r="B47" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131501252</v>
       </c>
       <c r="B48" t="n">
-        <v>80414</v>
+        <v>80416</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131501215</v>
+        <v>131501226</v>
       </c>
       <c r="B50" t="n">
-        <v>80283</v>
+        <v>80341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5601,21 +5601,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>387585</v>
+        <v>387577</v>
       </c>
       <c r="R50" t="n">
-        <v>6618100</v>
+        <v>6617725</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5687,10 +5687,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131501226</v>
+        <v>131501225</v>
       </c>
       <c r="B51" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>387577</v>
+        <v>387573</v>
       </c>
       <c r="R51" t="n">
-        <v>6617725</v>
+        <v>6617731</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131501225</v>
+        <v>131501215</v>
       </c>
       <c r="B52" t="n">
-        <v>80339</v>
+        <v>80285</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5795,21 +5795,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>387573</v>
+        <v>387585</v>
       </c>
       <c r="R52" t="n">
-        <v>6617731</v>
+        <v>6618100</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5884,7 +5884,7 @@
         <v>131501263</v>
       </c>
       <c r="B53" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>131501218</v>
       </c>
       <c r="B54" t="n">
-        <v>80283</v>
+        <v>80285</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>131501236</v>
       </c>
       <c r="B55" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>131501210</v>
       </c>
       <c r="B56" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>131501193</v>
       </c>
       <c r="B57" t="n">
-        <v>80252</v>
+        <v>80254</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>131819716</v>
       </c>
       <c r="B58" t="n">
-        <v>91867</v>
+        <v>91869</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>131822720</v>
       </c>
       <c r="B59" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>131816381</v>
       </c>
       <c r="B60" t="n">
-        <v>91867</v>
+        <v>91869</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>131819186</v>
       </c>
       <c r="B61" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>131821732</v>
       </c>
       <c r="B62" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>131815937</v>
       </c>
       <c r="B63" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>131822763</v>
       </c>
       <c r="B64" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>131819629</v>
       </c>
       <c r="B65" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>131820869</v>
       </c>
       <c r="B66" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7444,48 +7444,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B67" t="n">
-        <v>92306</v>
+        <v>57105</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R67" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7514,7 +7523,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7524,7 +7533,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7539,69 +7553,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B68" t="n">
-        <v>57103</v>
+        <v>92308</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R68" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7630,7 +7635,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7640,12 +7645,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7675,7 +7675,7 @@
         <v>131820835</v>
       </c>
       <c r="B69" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>131820604</v>
       </c>
       <c r="B70" t="n">
-        <v>80414</v>
+        <v>80416</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7885,48 +7885,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131821338</v>
+        <v>131820383</v>
       </c>
       <c r="B71" t="n">
-        <v>75380</v>
+        <v>93174</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387631</v>
+        <v>387672</v>
       </c>
       <c r="R71" t="n">
-        <v>6618098</v>
+        <v>6617684</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7980,22 +7980,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131815985</v>
+        <v>131821338</v>
       </c>
       <c r="B72" t="n">
-        <v>80408</v>
+        <v>75382</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8003,37 +8003,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387618</v>
+        <v>387631</v>
       </c>
       <c r="R72" t="n">
-        <v>6618030</v>
+        <v>6618098</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8087,57 +8087,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131820383</v>
+        <v>131815985</v>
       </c>
       <c r="B73" t="n">
-        <v>93172</v>
+        <v>80410</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387672</v>
+        <v>387618</v>
       </c>
       <c r="R73" t="n">
-        <v>6617684</v>
+        <v>6618030</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8209,7 +8209,7 @@
         <v>131817086</v>
       </c>
       <c r="B74" t="n">
-        <v>90883</v>
+        <v>90885</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>131821100</v>
       </c>
       <c r="B75" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8445,10 +8445,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131816272</v>
+        <v>131820504</v>
       </c>
       <c r="B76" t="n">
-        <v>8444</v>
+        <v>91811</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8456,48 +8456,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387612</v>
+        <v>387672</v>
       </c>
       <c r="R76" t="n">
-        <v>6618060</v>
+        <v>6617684</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,7 +8515,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8539,7 +8525,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8566,10 +8552,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131820504</v>
+        <v>131816272</v>
       </c>
       <c r="B77" t="n">
-        <v>91809</v>
+        <v>8444</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8577,34 +8563,48 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387672</v>
+        <v>387612</v>
       </c>
       <c r="R77" t="n">
-        <v>6617684</v>
+        <v>6618060</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8676,7 +8676,7 @@
         <v>131816249</v>
       </c>
       <c r="B78" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>131823453</v>
       </c>
       <c r="B79" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>131820532</v>
       </c>
       <c r="B81" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>131820813</v>
       </c>
       <c r="B83" t="n">
-        <v>80414</v>
+        <v>80416</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1817,53 +1817,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B12" t="n">
-        <v>57911</v>
+        <v>80341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R12" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1922,45 +1914,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B13" t="n">
-        <v>80341</v>
+        <v>57911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R13" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131501242</v>
+        <v>131501239</v>
       </c>
       <c r="B27" t="n">
-        <v>80249</v>
+        <v>80254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6441</v>
+        <v>392</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387660</v>
+        <v>387579</v>
       </c>
       <c r="R27" t="n">
-        <v>6617886</v>
+        <v>6618064</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131501259</v>
+        <v>131501242</v>
       </c>
       <c r="B28" t="n">
-        <v>80416</v>
+        <v>80249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6441</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387611</v>
+        <v>387660</v>
       </c>
       <c r="R28" t="n">
-        <v>6617519</v>
+        <v>6617886</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3467,6 +3467,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3485,32 +3486,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131501239</v>
+        <v>131501259</v>
       </c>
       <c r="B29" t="n">
-        <v>80254</v>
+        <v>80416</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3520,10 +3521,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387579</v>
+        <v>387611</v>
       </c>
       <c r="R29" t="n">
-        <v>6618064</v>
+        <v>6617519</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3564,7 +3565,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -1427,32 +1427,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131501250</v>
+        <v>131501213</v>
       </c>
       <c r="B8" t="n">
-        <v>80254</v>
+        <v>80285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387571</v>
+        <v>387596</v>
       </c>
       <c r="R8" t="n">
-        <v>6618050</v>
+        <v>6618070</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1506,7 +1506,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1525,32 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131501249</v>
+        <v>131501235</v>
       </c>
       <c r="B9" t="n">
-        <v>80254</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1560,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387577</v>
+        <v>387569</v>
       </c>
       <c r="R9" t="n">
-        <v>6618050</v>
+        <v>6617686</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1604,7 +1603,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1623,32 +1621,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131501213</v>
+        <v>131501250</v>
       </c>
       <c r="B10" t="n">
-        <v>80285</v>
+        <v>80254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1658,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387596</v>
+        <v>387571</v>
       </c>
       <c r="R10" t="n">
-        <v>6618070</v>
+        <v>6618050</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1702,6 +1700,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1720,32 +1719,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131501235</v>
+        <v>131501249</v>
       </c>
       <c r="B11" t="n">
-        <v>79276</v>
+        <v>80254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387569</v>
+        <v>387577</v>
       </c>
       <c r="R11" t="n">
-        <v>6617686</v>
+        <v>6618050</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1799,6 +1798,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1817,45 +1817,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131501230</v>
+        <v>131501203</v>
       </c>
       <c r="B12" t="n">
-        <v>80341</v>
+        <v>57911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387545</v>
+        <v>387626</v>
       </c>
       <c r="R12" t="n">
-        <v>6617619</v>
+        <v>6617753</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1914,53 +1922,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131501203</v>
+        <v>131501230</v>
       </c>
       <c r="B13" t="n">
-        <v>57911</v>
+        <v>80341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387626</v>
+        <v>387545</v>
       </c>
       <c r="R13" t="n">
-        <v>6617753</v>
+        <v>6617619</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131501247</v>
+        <v>131501195</v>
       </c>
       <c r="B14" t="n">
-        <v>80254</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387568</v>
+        <v>387619</v>
       </c>
       <c r="R14" t="n">
-        <v>6618040</v>
+        <v>6618073</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2098,7 +2098,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2117,32 +2116,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131501195</v>
+        <v>131501247</v>
       </c>
       <c r="B15" t="n">
-        <v>91811</v>
+        <v>80254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>392</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2152,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387619</v>
+        <v>387568</v>
       </c>
       <c r="R15" t="n">
-        <v>6618073</v>
+        <v>6618040</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2196,6 +2195,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -3583,45 +3583,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131501253</v>
+        <v>131501208</v>
       </c>
       <c r="B30" t="n">
-        <v>80416</v>
+        <v>57911</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387583</v>
+        <v>387565</v>
       </c>
       <c r="R30" t="n">
-        <v>6618100</v>
+        <v>6617589</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3654,6 +3662,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3680,45 +3693,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131501223</v>
+        <v>131501211</v>
       </c>
       <c r="B31" t="n">
-        <v>83241</v>
+        <v>57911</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387587</v>
+        <v>387554</v>
       </c>
       <c r="R31" t="n">
-        <v>6617454</v>
+        <v>6617473</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3777,7 +3798,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131501208</v>
+        <v>131501204</v>
       </c>
       <c r="B32" t="n">
         <v>57911</v>
@@ -3820,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387565</v>
+        <v>387618</v>
       </c>
       <c r="R32" t="n">
-        <v>6617589</v>
+        <v>6618118</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3887,53 +3908,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131501204</v>
+        <v>131501253</v>
       </c>
       <c r="B33" t="n">
-        <v>57911</v>
+        <v>80416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387618</v>
+        <v>387583</v>
       </c>
       <c r="R33" t="n">
-        <v>6618118</v>
+        <v>6618100</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3966,11 +3979,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3997,53 +4005,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131501211</v>
+        <v>131501223</v>
       </c>
       <c r="B34" t="n">
-        <v>57911</v>
+        <v>83241</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387554</v>
+        <v>387587</v>
       </c>
       <c r="R34" t="n">
-        <v>6617473</v>
+        <v>6617454</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4298,45 +4298,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131501255</v>
+        <v>131501222</v>
       </c>
       <c r="B37" t="n">
-        <v>80416</v>
+        <v>92268</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387660</v>
+        <v>387619</v>
       </c>
       <c r="R37" t="n">
-        <v>6617892</v>
+        <v>6618071</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4377,6 +4380,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4395,48 +4399,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131501222</v>
+        <v>131501255</v>
       </c>
       <c r="B38" t="n">
-        <v>92268</v>
+        <v>80416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387619</v>
+        <v>387660</v>
       </c>
       <c r="R38" t="n">
-        <v>6618071</v>
+        <v>6617892</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4477,7 +4478,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131501234</v>
+        <v>131501248</v>
       </c>
       <c r="B39" t="n">
-        <v>79276</v>
+        <v>80254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387610</v>
+        <v>387575</v>
       </c>
       <c r="R39" t="n">
-        <v>6617762</v>
+        <v>6618043</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4575,6 +4575,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4593,7 +4594,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131501248</v>
+        <v>131501238</v>
       </c>
       <c r="B40" t="n">
         <v>80254</v>
@@ -4628,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387575</v>
+        <v>387572</v>
       </c>
       <c r="R40" t="n">
-        <v>6618043</v>
+        <v>6618061</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4691,7 +4692,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131501238</v>
+        <v>131501245</v>
       </c>
       <c r="B41" t="n">
         <v>80254</v>
@@ -4726,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387572</v>
+        <v>387569</v>
       </c>
       <c r="R41" t="n">
-        <v>6618061</v>
+        <v>6617723</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4789,32 +4790,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131501245</v>
+        <v>131501234</v>
       </c>
       <c r="B42" t="n">
-        <v>80254</v>
+        <v>79276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387569</v>
+        <v>387610</v>
       </c>
       <c r="R42" t="n">
-        <v>6617723</v>
+        <v>6617762</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4868,7 +4869,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4887,45 +4887,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131501196</v>
+        <v>131501209</v>
       </c>
       <c r="B43" t="n">
-        <v>91811</v>
+        <v>57911</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387554</v>
+        <v>387543</v>
       </c>
       <c r="R43" t="n">
-        <v>6617465</v>
+        <v>6617571</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4958,6 +4966,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4984,32 +4997,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131501240</v>
+        <v>131501196</v>
       </c>
       <c r="B44" t="n">
-        <v>80254</v>
+        <v>91811</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,10 +5032,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387597</v>
+        <v>387554</v>
       </c>
       <c r="R44" t="n">
-        <v>6618067</v>
+        <v>6617465</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5063,7 +5076,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5082,10 +5094,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131501220</v>
+        <v>131501240</v>
       </c>
       <c r="B45" t="n">
-        <v>92308</v>
+        <v>80254</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,21 +5105,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>392</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5117,10 +5129,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387620</v>
+        <v>387597</v>
       </c>
       <c r="R45" t="n">
-        <v>6618075</v>
+        <v>6618067</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5161,6 +5173,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5179,53 +5192,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131501209</v>
+        <v>131501220</v>
       </c>
       <c r="B46" t="n">
-        <v>57911</v>
+        <v>92308</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergtjärn, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>387543</v>
+        <v>387620</v>
       </c>
       <c r="R46" t="n">
-        <v>6617571</v>
+        <v>6618075</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5258,11 +5263,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5590,7 +5590,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131501226</v>
+        <v>131501225</v>
       </c>
       <c r="B50" t="n">
         <v>80341</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>387577</v>
+        <v>387573</v>
       </c>
       <c r="R50" t="n">
-        <v>6617725</v>
+        <v>6617731</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5687,10 +5687,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131501225</v>
+        <v>131501215</v>
       </c>
       <c r="B51" t="n">
-        <v>80341</v>
+        <v>80285</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5698,21 +5698,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>387573</v>
+        <v>387585</v>
       </c>
       <c r="R51" t="n">
-        <v>6617731</v>
+        <v>6618100</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131501215</v>
+        <v>131501226</v>
       </c>
       <c r="B52" t="n">
-        <v>80285</v>
+        <v>80341</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5795,21 +5795,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>387585</v>
+        <v>387577</v>
       </c>
       <c r="R52" t="n">
-        <v>6618100</v>
+        <v>6617725</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5881,32 +5881,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131501263</v>
+        <v>131501218</v>
       </c>
       <c r="B53" t="n">
-        <v>80254</v>
+        <v>80285</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387610</v>
+        <v>387575</v>
       </c>
       <c r="R53" t="n">
-        <v>6617561</v>
+        <v>6617729</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5960,7 +5960,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5979,32 +5978,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131501218</v>
+        <v>131501236</v>
       </c>
       <c r="B54" t="n">
-        <v>80285</v>
+        <v>79276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6014,10 +6013,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387575</v>
+        <v>387557</v>
       </c>
       <c r="R54" t="n">
-        <v>6617729</v>
+        <v>6617549</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6076,32 +6075,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131501236</v>
+        <v>131501263</v>
       </c>
       <c r="B55" t="n">
-        <v>79276</v>
+        <v>80254</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6111,10 +6110,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387557</v>
+        <v>387610</v>
       </c>
       <c r="R55" t="n">
-        <v>6617549</v>
+        <v>6617561</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6155,6 +6154,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7444,57 +7444,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B67" t="n">
-        <v>57105</v>
+        <v>92308</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R67" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7523,7 +7514,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7533,12 +7524,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,60 +7539,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B68" t="n">
-        <v>92308</v>
+        <v>57105</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R68" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7635,7 +7630,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7645,7 +7640,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7885,48 +7885,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131820383</v>
+        <v>131821338</v>
       </c>
       <c r="B71" t="n">
-        <v>93174</v>
+        <v>75382</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387672</v>
+        <v>387631</v>
       </c>
       <c r="R71" t="n">
-        <v>6617684</v>
+        <v>6618098</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7980,22 +7980,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131821338</v>
+        <v>131815985</v>
       </c>
       <c r="B72" t="n">
-        <v>75382</v>
+        <v>80410</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8003,37 +8003,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387631</v>
+        <v>387618</v>
       </c>
       <c r="R72" t="n">
-        <v>6618098</v>
+        <v>6618030</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8087,57 +8087,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131815985</v>
+        <v>131820383</v>
       </c>
       <c r="B73" t="n">
-        <v>80410</v>
+        <v>93174</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387618</v>
+        <v>387672</v>
       </c>
       <c r="R73" t="n">
-        <v>6618030</v>
+        <v>6617684</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -6736,10 +6736,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131819186</v>
+        <v>131821732</v>
       </c>
       <c r="B61" t="n">
-        <v>57102</v>
+        <v>80341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6747,53 +6747,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>387618</v>
+        <v>387538</v>
       </c>
       <c r="R61" t="n">
-        <v>6618030</v>
+        <v>6617660</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,7 +6806,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6835,12 +6816,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6867,10 +6843,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131821732</v>
+        <v>131819186</v>
       </c>
       <c r="B62" t="n">
-        <v>80341</v>
+        <v>57102</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6878,34 +6854,53 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387538</v>
+        <v>387618</v>
       </c>
       <c r="R62" t="n">
-        <v>6617660</v>
+        <v>6618030</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6937,7 +6932,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6947,7 +6942,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7444,48 +7444,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B67" t="n">
-        <v>92308</v>
+        <v>57105</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R67" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7514,7 +7523,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7524,7 +7533,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7539,69 +7553,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B68" t="n">
-        <v>57105</v>
+        <v>92308</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R68" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7630,7 +7635,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7640,12 +7645,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7885,10 +7885,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131821338</v>
+        <v>131815985</v>
       </c>
       <c r="B71" t="n">
-        <v>75382</v>
+        <v>80410</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7896,37 +7896,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387631</v>
+        <v>387618</v>
       </c>
       <c r="R71" t="n">
-        <v>6618098</v>
+        <v>6618030</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7980,22 +7980,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131815985</v>
+        <v>131821338</v>
       </c>
       <c r="B72" t="n">
-        <v>80410</v>
+        <v>75382</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8003,37 +8003,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387618</v>
+        <v>387631</v>
       </c>
       <c r="R72" t="n">
-        <v>6618030</v>
+        <v>6618098</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8087,12 +8087,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -7444,57 +7444,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B67" t="n">
-        <v>57105</v>
+        <v>92308</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R67" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7523,7 +7514,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7533,12 +7524,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,60 +7539,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B68" t="n">
-        <v>92308</v>
+        <v>57105</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R68" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7635,7 +7630,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7645,7 +7640,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -7444,48 +7444,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B67" t="n">
-        <v>92308</v>
+        <v>57105</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R67" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7514,7 +7523,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7524,7 +7533,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7539,69 +7553,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B68" t="n">
-        <v>57105</v>
+        <v>92308</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R68" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7630,7 +7635,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7640,12 +7645,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -6736,10 +6736,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131821732</v>
+        <v>131819186</v>
       </c>
       <c r="B61" t="n">
-        <v>80341</v>
+        <v>57102</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6747,34 +6747,53 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>387538</v>
+        <v>387618</v>
       </c>
       <c r="R61" t="n">
-        <v>6617660</v>
+        <v>6618030</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6806,7 +6825,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6816,7 +6835,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6843,10 +6867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131819186</v>
+        <v>131821732</v>
       </c>
       <c r="B62" t="n">
-        <v>57102</v>
+        <v>80341</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6854,53 +6878,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387618</v>
+        <v>387538</v>
       </c>
       <c r="R62" t="n">
-        <v>6618030</v>
+        <v>6617660</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,7 +6937,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6942,12 +6947,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7885,10 +7885,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131815985</v>
+        <v>131821338</v>
       </c>
       <c r="B71" t="n">
-        <v>80410</v>
+        <v>75382</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7896,37 +7896,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387618</v>
+        <v>387631</v>
       </c>
       <c r="R71" t="n">
-        <v>6618030</v>
+        <v>6618098</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7980,22 +7980,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131821338</v>
+        <v>131815985</v>
       </c>
       <c r="B72" t="n">
-        <v>75382</v>
+        <v>80410</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8003,37 +8003,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387631</v>
+        <v>387618</v>
       </c>
       <c r="R72" t="n">
-        <v>6618098</v>
+        <v>6618030</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8087,12 +8087,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -6381,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131819716</v>
+        <v>131822720</v>
       </c>
       <c r="B58" t="n">
-        <v>91869</v>
+        <v>57945</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6416,7 +6416,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6425,10 +6430,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>387662</v>
+        <v>387686</v>
       </c>
       <c r="R58" t="n">
-        <v>6617924</v>
+        <v>6617861</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6460,7 +6465,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6470,7 +6475,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6497,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131822720</v>
+        <v>131819716</v>
       </c>
       <c r="B59" t="n">
-        <v>57911</v>
+        <v>91905</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6508,21 +6513,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6532,12 +6537,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387686</v>
+        <v>387662</v>
       </c>
       <c r="R59" t="n">
-        <v>6617861</v>
+        <v>6617924</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6621,7 +6621,7 @@
         <v>131816381</v>
       </c>
       <c r="B60" t="n">
-        <v>91869</v>
+        <v>91905</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>131819186</v>
       </c>
       <c r="B61" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>131821732</v>
       </c>
       <c r="B62" t="n">
-        <v>80341</v>
+        <v>80375</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>131815937</v>
       </c>
       <c r="B63" t="n">
-        <v>80341</v>
+        <v>80375</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>131822763</v>
       </c>
       <c r="B64" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>131819629</v>
       </c>
       <c r="B65" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>131820869</v>
       </c>
       <c r="B66" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7444,57 +7444,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131820899</v>
+        <v>131822775</v>
       </c>
       <c r="B67" t="n">
-        <v>57105</v>
+        <v>92344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387516</v>
+        <v>387628</v>
       </c>
       <c r="R67" t="n">
-        <v>6617582</v>
+        <v>6618089</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7523,7 +7514,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7533,12 +7524,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spelspillning</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,60 +7539,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131822775</v>
+        <v>131820899</v>
       </c>
       <c r="B68" t="n">
-        <v>92308</v>
+        <v>57139</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>102613</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387628</v>
+        <v>387516</v>
       </c>
       <c r="R68" t="n">
-        <v>6618089</v>
+        <v>6617582</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7635,7 +7630,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7645,7 +7640,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Spelspillning</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7660,12 +7660,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7675,7 +7675,7 @@
         <v>131820835</v>
       </c>
       <c r="B69" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>131820604</v>
       </c>
       <c r="B70" t="n">
-        <v>80416</v>
+        <v>80450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>131821338</v>
       </c>
       <c r="B71" t="n">
-        <v>75382</v>
+        <v>75416</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>131815985</v>
       </c>
       <c r="B72" t="n">
-        <v>80410</v>
+        <v>80444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>131820383</v>
       </c>
       <c r="B73" t="n">
-        <v>93174</v>
+        <v>93210</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8206,59 +8206,62 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131817086</v>
+        <v>131821100</v>
       </c>
       <c r="B74" t="n">
-        <v>90885</v>
+        <v>99090</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>889</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387612</v>
+        <v>387541</v>
       </c>
       <c r="R74" t="n">
-        <v>6618032</v>
+        <v>6617620</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8287,7 +8290,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8297,7 +8300,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8312,74 +8315,71 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131821100</v>
+        <v>131817086</v>
       </c>
       <c r="B75" t="n">
-        <v>99054</v>
+        <v>90921</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>889</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387541</v>
+        <v>387612</v>
       </c>
       <c r="R75" t="n">
-        <v>6617620</v>
+        <v>6618032</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8433,12 +8433,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8448,7 +8448,7 @@
         <v>131820504</v>
       </c>
       <c r="B76" t="n">
-        <v>91811</v>
+        <v>91847</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>131816249</v>
       </c>
       <c r="B78" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>131823453</v>
       </c>
       <c r="B79" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>131820532</v>
       </c>
       <c r="B81" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>131820813</v>
       </c>
       <c r="B83" t="n">
-        <v>80416</v>
+        <v>80450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -6381,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131822720</v>
+        <v>131819716</v>
       </c>
       <c r="B58" t="n">
-        <v>57945</v>
+        <v>91913</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6416,12 +6416,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6430,10 +6425,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>387686</v>
+        <v>387662</v>
       </c>
       <c r="R58" t="n">
-        <v>6617861</v>
+        <v>6617924</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6465,7 +6460,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6475,7 +6470,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6502,10 +6497,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131819716</v>
+        <v>131822720</v>
       </c>
       <c r="B59" t="n">
-        <v>91910</v>
+        <v>57945</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,21 +6508,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6537,7 +6532,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387662</v>
+        <v>387686</v>
       </c>
       <c r="R59" t="n">
-        <v>6617924</v>
+        <v>6617861</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6621,7 +6621,7 @@
         <v>131816381</v>
       </c>
       <c r="B60" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>131821732</v>
       </c>
       <c r="B62" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>131815937</v>
       </c>
       <c r="B63" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>131820869</v>
       </c>
       <c r="B65" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>131822775</v>
       </c>
       <c r="B67" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>131820835</v>
       </c>
       <c r="B69" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>131820604</v>
       </c>
       <c r="B70" t="n">
-        <v>80455</v>
+        <v>80457</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7885,48 +7885,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131821338</v>
+        <v>131820383</v>
       </c>
       <c r="B71" t="n">
-        <v>75421</v>
+        <v>93218</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387631</v>
+        <v>387672</v>
       </c>
       <c r="R71" t="n">
-        <v>6618098</v>
+        <v>6617684</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7980,22 +7980,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131815985</v>
+        <v>131821338</v>
       </c>
       <c r="B72" t="n">
-        <v>80449</v>
+        <v>75423</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8003,37 +8003,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387618</v>
+        <v>387631</v>
       </c>
       <c r="R72" t="n">
-        <v>6618030</v>
+        <v>6618098</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8087,57 +8087,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131820383</v>
+        <v>131815985</v>
       </c>
       <c r="B73" t="n">
-        <v>93215</v>
+        <v>80451</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387672</v>
+        <v>387618</v>
       </c>
       <c r="R73" t="n">
-        <v>6617684</v>
+        <v>6618030</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8209,7 +8209,7 @@
         <v>131817086</v>
       </c>
       <c r="B74" t="n">
-        <v>90926</v>
+        <v>90929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>131821100</v>
       </c>
       <c r="B75" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>131820504</v>
       </c>
       <c r="B76" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>131820532</v>
       </c>
       <c r="B81" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>131820813</v>
       </c>
       <c r="B83" t="n">
-        <v>80455</v>
+        <v>80457</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -7207,57 +7207,67 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131820869</v>
+        <v>131819629</v>
       </c>
       <c r="B65" t="n">
-        <v>99098</v>
+        <v>57136</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>387592</v>
+        <v>387662</v>
       </c>
       <c r="R65" t="n">
-        <v>6618084</v>
+        <v>6617924</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7284,9 +7294,24 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7301,79 +7326,69 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131819629</v>
+        <v>131820869</v>
       </c>
       <c r="B66" t="n">
-        <v>57136</v>
+        <v>99098</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387662</v>
+        <v>387592</v>
       </c>
       <c r="R66" t="n">
-        <v>6617924</v>
+        <v>6618084</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7400,24 +7415,9 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7432,12 +7432,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7885,48 +7885,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131820383</v>
+        <v>131821338</v>
       </c>
       <c r="B71" t="n">
-        <v>93218</v>
+        <v>75423</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387672</v>
+        <v>387631</v>
       </c>
       <c r="R71" t="n">
-        <v>6617684</v>
+        <v>6618098</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7980,22 +7980,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Daniel Berger</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131821338</v>
+        <v>131815985</v>
       </c>
       <c r="B72" t="n">
-        <v>75423</v>
+        <v>80451</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8003,37 +8003,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387631</v>
+        <v>387618</v>
       </c>
       <c r="R72" t="n">
-        <v>6618098</v>
+        <v>6618030</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8087,57 +8087,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Berger</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131815985</v>
+        <v>131820383</v>
       </c>
       <c r="B73" t="n">
-        <v>80451</v>
+        <v>93218</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387618</v>
+        <v>387672</v>
       </c>
       <c r="R73" t="n">
-        <v>6618030</v>
+        <v>6617684</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8445,10 +8445,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131820504</v>
+        <v>131816272</v>
       </c>
       <c r="B76" t="n">
-        <v>91855</v>
+        <v>8444</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8456,34 +8456,48 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387672</v>
+        <v>387612</v>
       </c>
       <c r="R76" t="n">
-        <v>6617684</v>
+        <v>6618060</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8515,7 +8529,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8525,7 +8539,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8552,10 +8566,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131816272</v>
+        <v>131820504</v>
       </c>
       <c r="B77" t="n">
-        <v>8444</v>
+        <v>91855</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8563,48 +8577,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387612</v>
+        <v>387672</v>
       </c>
       <c r="R77" t="n">
-        <v>6618060</v>
+        <v>6617684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 5535-2026 artfynd.xlsx
+++ b/artfynd/A 5535-2026 artfynd.xlsx
@@ -7207,67 +7207,57 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131819629</v>
+        <v>131820869</v>
       </c>
       <c r="B65" t="n">
-        <v>57136</v>
+        <v>99098</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>387662</v>
+        <v>387592</v>
       </c>
       <c r="R65" t="n">
-        <v>6617924</v>
+        <v>6618084</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7294,24 +7284,9 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7326,69 +7301,79 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Lisa Ingwall-King</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131820869</v>
+        <v>131819629</v>
       </c>
       <c r="B66" t="n">
-        <v>99098</v>
+        <v>57136</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387592</v>
+        <v>387662</v>
       </c>
       <c r="R66" t="n">
-        <v>6618084</v>
+        <v>6617924</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7415,9 +7400,24 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7432,12 +7432,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Ingwall-King</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8206,59 +8206,62 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131817086</v>
+        <v>131821100</v>
       </c>
       <c r="B74" t="n">
-        <v>90929</v>
+        <v>99098</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>889</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Noltomten, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387612</v>
+        <v>387541</v>
       </c>
       <c r="R74" t="n">
-        <v>6618032</v>
+        <v>6617620</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8287,7 +8290,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8297,7 +8300,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8312,74 +8315,71 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Martin Eneling</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131821100</v>
+        <v>131817086</v>
       </c>
       <c r="B75" t="n">
-        <v>99098</v>
+        <v>90929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>889</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Noltomten, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387541</v>
+        <v>387612</v>
       </c>
       <c r="R75" t="n">
-        <v>6617620</v>
+        <v>6618032</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8433,12 +8433,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Martin Eneling</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
